--- a/2022 data/excel_outputs/152_boothwise_data.xlsx
+++ b/2022 data/excel_outputs/152_boothwise_data.xlsx
@@ -14,714 +14,1368 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="454" uniqueCount="259">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="479" uniqueCount="477">
   <si>
     <t>AC 152 Booth-wise Data</t>
   </si>
   <si>
+    <t>Unnamed: 1</t>
+  </si>
+  <si>
+    <t>Unnamed: 2</t>
+  </si>
+  <si>
+    <t>Unnamed: 3</t>
+  </si>
+  <si>
+    <t>Unnamed: 4</t>
+  </si>
+  <si>
+    <t>Unnamed: 5</t>
+  </si>
+  <si>
+    <t>Unnamed: 6</t>
+  </si>
+  <si>
+    <t>Unnamed: 7</t>
+  </si>
+  <si>
+    <t>Unnamed: 8</t>
+  </si>
+  <si>
+    <t>Unnamed: 9</t>
+  </si>
+  <si>
+    <t>Unnamed: 10</t>
+  </si>
+  <si>
+    <t>Unnamed: 11</t>
+  </si>
+  <si>
+    <t>Unnamed: 12</t>
+  </si>
+  <si>
+    <t>Unnamed: 13</t>
+  </si>
+  <si>
+    <t>Unnamed: 14</t>
+  </si>
+  <si>
+    <t>Unnamed: 15</t>
+  </si>
+  <si>
+    <t>Unnamed: 16</t>
+  </si>
+  <si>
+    <t>Unnamed: 17</t>
+  </si>
+  <si>
+    <t>Unnamed: 18</t>
+  </si>
+  <si>
+    <t>Unnamed: 19</t>
+  </si>
+  <si>
+    <t>Unnamed: 20</t>
+  </si>
+  <si>
+    <t>Unnamed: 21</t>
+  </si>
+  <si>
+    <t>Unnamed: 22</t>
+  </si>
+  <si>
+    <t>Unnamed: 23</t>
+  </si>
+  <si>
+    <t>Unnamed: 24</t>
+  </si>
+  <si>
+    <t>Unnamed: 25</t>
+  </si>
+  <si>
     <t>BOOTH ID</t>
   </si>
   <si>
     <t>POLLING STATION NAME</t>
   </si>
   <si>
-    <t>###################</t>
-  </si>
-  <si>
-    <t>############### ##### 1</t>
-  </si>
-  <si>
-    <t>############### #####.2</t>
-  </si>
-  <si>
-    <t>################ #0 #######</t>
-  </si>
-  <si>
-    <t>###############</t>
-  </si>
-  <si>
-    <t>##############</t>
-  </si>
-  <si>
-    <t>####### ###############</t>
-  </si>
-  <si>
-    <t>################## ############# ########</t>
-  </si>
-  <si>
-    <t>################</t>
-  </si>
-  <si>
-    <t>############## #########</t>
-  </si>
-  <si>
-    <t>################ ####.1</t>
-  </si>
-  <si>
-    <t>################ ####.2</t>
-  </si>
-  <si>
-    <t>##### ####### #######</t>
-  </si>
-  <si>
-    <t>######## ###### #####</t>
-  </si>
-  <si>
-    <t>############## ####.1</t>
-  </si>
-  <si>
-    <t>############## ####.2</t>
-  </si>
-  <si>
-    <t>############## ####.3</t>
-  </si>
-  <si>
-    <t>######### ######</t>
-  </si>
-  <si>
-    <t>######## ######</t>
-  </si>
-  <si>
-    <t>################# ####.1</t>
-  </si>
-  <si>
-    <t>################# ####.2</t>
-  </si>
-  <si>
-    <t>############### ####.1</t>
-  </si>
-  <si>
-    <t>############### ####.2</t>
-  </si>
-  <si>
-    <t>############### ####.3</t>
-  </si>
-  <si>
-    <t>############ ############ ####.1</t>
-  </si>
-  <si>
-    <t>############ ############ ####.2</t>
-  </si>
-  <si>
-    <t>############ ############ ####.3</t>
-  </si>
-  <si>
-    <t>####0##0####### ####.1</t>
-  </si>
-  <si>
-    <t>####0##0####### ####.2</t>
-  </si>
-  <si>
-    <t>######## ####### #######</t>
-  </si>
-  <si>
-    <t>##### ### #######</t>
-  </si>
-  <si>
-    <t>####0##0 ######</t>
-  </si>
-  <si>
-    <t>############### #0 ######</t>
-  </si>
-  <si>
-    <t>####0##0########</t>
-  </si>
-  <si>
-    <t>####0##0##### ## ########### #### #0### 1</t>
-  </si>
-  <si>
-    <t>####0##0##### ## ########### #### #0##0 2</t>
-  </si>
-  <si>
-    <t>####0##0 #### ##########</t>
-  </si>
-  <si>
-    <t>################ ######## #0########</t>
-  </si>
-  <si>
-    <t>####0##0 ########</t>
-  </si>
-  <si>
-    <t>######## ####### ## #### ##### ####</t>
-  </si>
-  <si>
-    <t>############### ## #### #### ####</t>
-  </si>
-  <si>
-    <t>################### ####.1</t>
-  </si>
-  <si>
-    <t>################### ####.2</t>
-  </si>
-  <si>
-    <t>#############</t>
-  </si>
-  <si>
-    <t>############### ##### ####</t>
-  </si>
-  <si>
-    <t>######## ##### ####.1</t>
-  </si>
-  <si>
-    <t>######## ##### ####.2</t>
-  </si>
-  <si>
-    <t>######## ############ ##### 1</t>
-  </si>
-  <si>
-    <t>######## ############ ##### 2</t>
-  </si>
-  <si>
-    <t>######## ######## #0 #########</t>
-  </si>
-  <si>
-    <t>######### ######### ####.1</t>
-  </si>
-  <si>
-    <t>######### ######### ####.2</t>
-  </si>
-  <si>
-    <t>######## ######## #0#########</t>
-  </si>
-  <si>
-    <t>############# ####.1</t>
-  </si>
-  <si>
-    <t>############# ####.2</t>
-  </si>
-  <si>
-    <t>######## ######### #### ####.1</t>
-  </si>
-  <si>
-    <t>######## ######### #### ####.2</t>
-  </si>
-  <si>
-    <t>######## ###### ##### 1</t>
-  </si>
-  <si>
-    <t>######## ###### ##### 2</t>
-  </si>
-  <si>
-    <t>######## ####### ## ########</t>
-  </si>
-  <si>
-    <t>######## #####</t>
-  </si>
-  <si>
-    <t>######## ############## ##### 1</t>
-  </si>
-  <si>
-    <t>######## ############## ##### 2</t>
-  </si>
-  <si>
-    <t>######## ##### ## ######## ####.1</t>
-  </si>
-  <si>
-    <t>######## ##### ## ######## ####.2</t>
-  </si>
-  <si>
-    <t>######## ######### ## ##### ####.1</t>
-  </si>
-  <si>
-    <t>######## ######### ## ##### ####.2</t>
-  </si>
-  <si>
-    <t>############# #### ####</t>
-  </si>
-  <si>
-    <t>############# ##### ########## ####</t>
-  </si>
-  <si>
-    <t>######## ######## ###### ####</t>
-  </si>
-  <si>
-    <t>######## ######## #### ####</t>
-  </si>
-  <si>
-    <t>############## #0 ######## ####.1</t>
-  </si>
-  <si>
-    <t>############## #0 ######## ####.2</t>
-  </si>
-  <si>
-    <t>######## ###########</t>
-  </si>
-  <si>
-    <t>######## ####### ####.1</t>
-  </si>
-  <si>
-    <t>######## ####### ####.2</t>
-  </si>
-  <si>
-    <t>######## #########</t>
-  </si>
-  <si>
-    <t>######## #######</t>
-  </si>
-  <si>
-    <t>######## ####### #0 ####### ####.1</t>
-  </si>
-  <si>
-    <t>######## ####### #0 ####### ####.2</t>
-  </si>
-  <si>
-    <t>######### ###### ####.1</t>
-  </si>
-  <si>
-    <t>######### ###### ####.2</t>
-  </si>
-  <si>
-    <t>######## ###### ## ######</t>
-  </si>
-  <si>
-    <t>######## ####</t>
-  </si>
-  <si>
-    <t>######## #### ####.1</t>
-  </si>
-  <si>
-    <t>######## #### ####.2</t>
-  </si>
-  <si>
-    <t>######## ###### ####.1</t>
-  </si>
-  <si>
-    <t>######## ###### ####.2</t>
-  </si>
-  <si>
-    <t>##### ### ######</t>
-  </si>
-  <si>
-    <t>######## ##### #0### 1</t>
-  </si>
-  <si>
-    <t>######## ##### ##### 2</t>
-  </si>
-  <si>
-    <t>######## ### ####.1</t>
-  </si>
-  <si>
-    <t>######## ### ####.2</t>
-  </si>
-  <si>
-    <t>######## ############</t>
-  </si>
-  <si>
-    <t>#### ######## #### ###### ######### ####.1 #####</t>
-  </si>
-  <si>
-    <t>#### ######## #### ###### ######### ####.2 #####</t>
-  </si>
-  <si>
-    <t>########## ### ## #####</t>
-  </si>
-  <si>
-    <t>######## ####### ##### ####</t>
-  </si>
-  <si>
-    <t>######## ##### ######</t>
-  </si>
-  <si>
-    <t>######## ########</t>
-  </si>
-  <si>
-    <t>######## ###### #0 ########</t>
-  </si>
-  <si>
-    <t>######### ########</t>
-  </si>
-  <si>
-    <t>######### #####</t>
-  </si>
-  <si>
-    <t>######## ########## ####.1</t>
-  </si>
-  <si>
-    <t>######## ########## ####.2</t>
-  </si>
-  <si>
-    <t>######## ##### ##### 1</t>
-  </si>
-  <si>
-    <t>######## ##### ### ####.1</t>
-  </si>
-  <si>
-    <t>######## ##### ### ####.2</t>
-  </si>
-  <si>
-    <t>######## ####### ###</t>
-  </si>
-  <si>
-    <t>######## ####### ######## ####</t>
-  </si>
-  <si>
-    <t>######## ####### #0 ####</t>
-  </si>
-  <si>
-    <t>######### ########## ####.1</t>
-  </si>
-  <si>
-    <t>######### ########## ####.2</t>
-  </si>
-  <si>
-    <t>######## ####### #0 #######</t>
-  </si>
-  <si>
-    <t>######## ######### ####.1</t>
-  </si>
-  <si>
-    <t>######## ######### ####.2</t>
-  </si>
-  <si>
-    <t>######## ######## ###### ####.1</t>
-  </si>
-  <si>
-    <t>######## ######## ###### ####.2</t>
-  </si>
-  <si>
-    <t>########## ##### #### ####</t>
-  </si>
-  <si>
-    <t>########## ##### ###### ####</t>
-  </si>
-  <si>
-    <t>######## ###### ####.3</t>
-  </si>
-  <si>
-    <t>######### ######## ####.2</t>
-  </si>
-  <si>
-    <t>#### ######### ######### ######## ####.1</t>
-  </si>
-  <si>
-    <t>#### ######### ######### ######## ####.2</t>
-  </si>
-  <si>
-    <t>######## ######## #0 ########</t>
-  </si>
-  <si>
-    <t>######## ### ### ###########</t>
-  </si>
-  <si>
-    <t>######### ##### ####.1</t>
-  </si>
-  <si>
-    <t>######### ##### ####.2</t>
-  </si>
-  <si>
-    <t>######### ##### ####.3</t>
-  </si>
-  <si>
-    <t>##### ###### ####### #####</t>
-  </si>
-  <si>
-    <t>############# ##### #0##0.1</t>
-  </si>
-  <si>
-    <t>############# ##### #0##0.2</t>
-  </si>
-  <si>
-    <t>################## ####.2</t>
-  </si>
-  <si>
-    <t>################## ####.3</t>
-  </si>
-  <si>
-    <t>################## ####.4</t>
-  </si>
-  <si>
-    <t>################## ####.5</t>
-  </si>
-  <si>
-    <t>################## ####.11</t>
-  </si>
-  <si>
-    <t>##0########## ###### ####.1</t>
-  </si>
-  <si>
-    <t>##0########## ###### ####.2</t>
-  </si>
-  <si>
-    <t>##0########## ###### ####.3</t>
-  </si>
-  <si>
-    <t>##0########## ###### ####.4</t>
-  </si>
-  <si>
-    <t>############# ###### ####.5</t>
-  </si>
-  <si>
-    <t>################# ###### ####.1</t>
-  </si>
-  <si>
-    <t>################# ###### ####.2</t>
-  </si>
-  <si>
-    <t>################# ###### ####.3</t>
-  </si>
-  <si>
-    <t>############### ### #### ### #### ###### ####.1</t>
-  </si>
-  <si>
-    <t>############### ### #### ### #### ###### ####.2</t>
-  </si>
-  <si>
-    <t>############### ### #### ### #### ###### ####.3</t>
-  </si>
-  <si>
-    <t>########### ### ########## #### ####### ###### ####.1</t>
-  </si>
-  <si>
-    <t>########### ### ########## #### ####### ###### ####.2</t>
-  </si>
-  <si>
-    <t>######### ####### ## ####.1</t>
-  </si>
-  <si>
-    <t>######### ####### ## ####.2</t>
-  </si>
-  <si>
-    <t>######### ####### ## ####.3</t>
-  </si>
-  <si>
-    <t>######## ###### ###### ####.1</t>
-  </si>
-  <si>
-    <t>######## ###### ###### ####.2</t>
-  </si>
-  <si>
-    <t>######## ######## ####.1</t>
-  </si>
-  <si>
-    <t>######## ######## ####.2</t>
-  </si>
-  <si>
-    <t>######## ####### ##### 1</t>
-  </si>
-  <si>
-    <t>######## ####### ##### 2</t>
-  </si>
-  <si>
-    <t>######## ######## ####### ####</t>
-  </si>
-  <si>
-    <t>######## ######## ########## ####</t>
-  </si>
-  <si>
-    <t>############ ## ####### #### ### 1</t>
-  </si>
-  <si>
-    <t>############ ## ####### #### ## 2</t>
-  </si>
-  <si>
-    <t>######## ###### ## ###### #### ## 1</t>
-  </si>
-  <si>
-    <t>######## ###### ## ###### #### ## 2</t>
-  </si>
-  <si>
-    <t>######## ####### #### ## 1</t>
-  </si>
-  <si>
-    <t>######## ####### #### ## 2</t>
-  </si>
-  <si>
-    <t>######### ####### ####.1</t>
-  </si>
-  <si>
-    <t>######### ####### ####.2</t>
-  </si>
-  <si>
-    <t>######### ########### ####.1</t>
-  </si>
-  <si>
-    <t>######### ########### ####.2</t>
-  </si>
-  <si>
-    <t>########## #######</t>
-  </si>
-  <si>
-    <t>######## ##### #######</t>
-  </si>
-  <si>
-    <t>######## ######## ### ##### 1</t>
-  </si>
-  <si>
-    <t>######## ######## ### ####.2</t>
-  </si>
-  <si>
-    <t>######## #### ####</t>
-  </si>
-  <si>
-    <t>######## ##### ## ###### ####</t>
-  </si>
-  <si>
-    <t>######## ##########</t>
-  </si>
-  <si>
-    <t>######## ##### ####.3</t>
-  </si>
-  <si>
-    <t>######## ####### ## ######</t>
-  </si>
-  <si>
-    <t>######## ##### ## ######</t>
-  </si>
-  <si>
-    <t>######## ######### ######## ####.1</t>
-  </si>
-  <si>
-    <t>######## ######### ######## ####.2</t>
-  </si>
-  <si>
-    <t>######## ###### ## ##### ####.1</t>
-  </si>
-  <si>
-    <t>######## ###### ## ##### ####.2</t>
-  </si>
-  <si>
-    <t>######## ###### ## #####</t>
-  </si>
-  <si>
-    <t>######## ####### ####</t>
-  </si>
-  <si>
-    <t>######## ####### ###### ####</t>
-  </si>
-  <si>
-    <t>######## ####### #### ####</t>
-  </si>
-  <si>
-    <t>######## ####### #0 ##########</t>
-  </si>
-  <si>
-    <t>######## ############# #0 ##########</t>
-  </si>
-  <si>
-    <t>######## #### ## ####### ####.1</t>
-  </si>
-  <si>
-    <t>######## #### ## ####### ####.2</t>
-  </si>
-  <si>
-    <t>######## ####### ##### 3</t>
-  </si>
-  <si>
-    <t>######### #### #### ###### ####</t>
-  </si>
-  <si>
-    <t>######### #### #### ####### ####</t>
-  </si>
-  <si>
-    <t>######## ######## ##### 1</t>
-  </si>
-  <si>
-    <t>######## ######## ##### 2</t>
-  </si>
-  <si>
-    <t>######## #### #### ####.1</t>
-  </si>
-  <si>
-    <t>######## #### #### ####.2</t>
-  </si>
-  <si>
-    <t>######## #### #### ####.3</t>
-  </si>
-  <si>
-    <t>######## ##</t>
-  </si>
-  <si>
-    <t>######### ######## ## #####</t>
-  </si>
-  <si>
-    <t>######## ####### ## ####### ####.1</t>
-  </si>
-  <si>
-    <t>######## ####### ## ####### ####.2</t>
-  </si>
-  <si>
-    <t>######## ###### #0###### ######</t>
-  </si>
-  <si>
-    <t>######## ###### ######</t>
-  </si>
-  <si>
-    <t>######### ####### ###</t>
-  </si>
-  <si>
-    <t>######## ###### #0 ####### ###</t>
-  </si>
-  <si>
-    <t>######## ##### ###### #0 ########</t>
-  </si>
-  <si>
-    <t>######## ##### ########</t>
-  </si>
-  <si>
-    <t>######## ####### ####.3</t>
-  </si>
-  <si>
-    <t>######## ####### ####.4</t>
-  </si>
-  <si>
-    <t>######## ###### ## #######</t>
-  </si>
-  <si>
-    <t>######## ######## ## ##### ####.1</t>
-  </si>
-  <si>
-    <t>######## ######## ## ##### ####.2</t>
-  </si>
-  <si>
-    <t>########### ###### #0 ######</t>
-  </si>
-  <si>
-    <t>######## ######### #0 ######</t>
-  </si>
-  <si>
-    <t>########### ###### ####.1</t>
-  </si>
-  <si>
-    <t>########### ###### ####.2</t>
-  </si>
-  <si>
-    <t>########### ###### ####.3</t>
-  </si>
-  <si>
-    <t>####0### ##### ######</t>
-  </si>
-  <si>
-    <t>######## ####### ##### ####.1</t>
-  </si>
-  <si>
-    <t>######## ####### ##### ####.2</t>
-  </si>
-  <si>
-    <t>######## ####### ##### ####.3</t>
-  </si>
-  <si>
-    <t>######## ###### ####### ####.1</t>
-  </si>
-  <si>
-    <t>######## ###### ####### ####.2</t>
-  </si>
-  <si>
-    <t>######## ######## ####.3</t>
-  </si>
-  <si>
-    <t>######### ######## ####.1</t>
-  </si>
-  <si>
-    <t>######## ###### ######## ####.1</t>
-  </si>
-  <si>
-    <t>######## ###### ######## ####.2</t>
-  </si>
-  <si>
-    <t>######## ####### ## ########## ####.1</t>
-  </si>
-  <si>
-    <t>######## ####### ## ########## ####.2</t>
+    <t>P.S.GOVINDAPUR</t>
+  </si>
+  <si>
+    <t>P.S.HAMIRAPUR</t>
+  </si>
+  <si>
+    <t>J.H.S.KUSAMAURA MO HAMIRPUR</t>
+  </si>
+  <si>
+    <t>P.S.NAVAGANVA</t>
+  </si>
+  <si>
+    <t>P.S.BHANAPUR</t>
+  </si>
+  <si>
+    <t>SARVODAYA U.M.S. BAMBHERA</t>
+  </si>
+  <si>
+    <t>P.S.MOHARPURVA MO GOVINDAPUR HARADOPATTI</t>
+  </si>
+  <si>
+    <t>P.S.HARIHARAPUR</t>
+  </si>
+  <si>
+    <t>P.S.BHAHURI MO GANESHAPUR</t>
+  </si>
+  <si>
+    <t>P.S.CHITAREHATA</t>
+  </si>
+  <si>
+    <t>P.S. JAYARAMAPUR KAMRA NO 1</t>
+  </si>
+  <si>
+    <t>P.S. JAYARAMPUR KAMRA NO 2</t>
+  </si>
+  <si>
+    <t>P.S. MANGUPUR KAMRA NO 1</t>
+  </si>
+  <si>
+    <t>GRAM SACHIVALAY MADHAVAPUR</t>
+  </si>
+  <si>
+    <t>P.S. JAITNAPUR</t>
+  </si>
+  <si>
+    <t>P.S. PRATAP BEHAD</t>
+  </si>
+  <si>
+    <t>P.S. SAIDAPUR</t>
+  </si>
+  <si>
+    <t>P.S. DARIYAPUR</t>
+  </si>
+  <si>
+    <t>P.S. BAHIRIMAU KAMRA NO 1</t>
+  </si>
+  <si>
+    <t>P.S. BAHIRIMAU KAMRA NO 2</t>
+  </si>
+  <si>
+    <t>P.S. MAHAKHRI</t>
+  </si>
+  <si>
+    <t>J.H.S. SUJAULIYA</t>
+  </si>
+  <si>
+    <t>P.S.BASANTAPUR KAMRA NO 1</t>
+  </si>
+  <si>
+    <t>P.S.BASANTAPUR KAMRA NO 2</t>
+  </si>
+  <si>
+    <t>P.S. SURAINCHA KAMRA NO 1</t>
+  </si>
+  <si>
+    <t>P.S. SURAINCHA KAMRA NO 2</t>
+  </si>
+  <si>
+    <t>P.S. NAVIN UNCHAKHERAKALAN KAMRA NO 1</t>
+  </si>
+  <si>
+    <t>P.S. NAVIN UCHANKHERAKALAN KAMRA NO 2</t>
+  </si>
+  <si>
+    <t>P.S. KOKANAMAU KAMRA NO 1</t>
+  </si>
+  <si>
+    <t>P.S. KOKANAMAU KAMRA NO 2</t>
+  </si>
+  <si>
+    <t>P.S. KASMANDA PURAB KAMRA</t>
+  </si>
+  <si>
+    <t>P.S. KASMANDA PASHIM KAMRA</t>
+  </si>
+  <si>
+    <t>SANKUL BHAVAN KASMANDA</t>
+  </si>
+  <si>
+    <t>P.S. KHURDA</t>
+  </si>
+  <si>
+    <t>J.H.S.PURAINA MO KHURDA</t>
+  </si>
+  <si>
+    <t>P.S. JODAURA KAMRA NO 1</t>
+  </si>
+  <si>
+    <t>P.S. JODAURA KAMRA NO 2</t>
+  </si>
+  <si>
+    <t>P.S. KURSANDA</t>
+  </si>
+  <si>
+    <t>P.S. PALIYA MO SARAIYABALDEV SINGH</t>
+  </si>
+  <si>
+    <t>P.S. NAVIN NYORAJAPUR</t>
+  </si>
+  <si>
+    <t>BH.V.M.U.M.VIDVALAY. KAMHARIYA M0 JAGADISHAPUR KAMRA NO 1</t>
+  </si>
+  <si>
+    <t>P.S.JAGADISHAPUR</t>
+  </si>
+  <si>
+    <t>P.S. DAULATPUR MO KAIMA UATTAR KAMRA</t>
+  </si>
+  <si>
+    <t>P.S. DAULATPUR MO KAIMA MADHY KAMRA</t>
+  </si>
+  <si>
+    <t>P.S. SARAVAJALALAPUR KAMRA NO 1</t>
+  </si>
+  <si>
+    <t>P.S. SARAVAJALALAPUR KAMRA NO 2</t>
+  </si>
+  <si>
+    <t>P.S. PALIYA</t>
+  </si>
+  <si>
+    <t>P.S. SHIVRA</t>
+  </si>
+  <si>
+    <t>P.S. FARIDAPUR MAHIPAT SINGH</t>
+  </si>
+  <si>
+    <t>P.S. MALETHU KAMRA NO 1</t>
+  </si>
+  <si>
+    <t>P.S. MALETHU KAMRA NO 2</t>
+  </si>
+  <si>
+    <t>P.S. KANDHAIMAHIMAPUR</t>
+  </si>
+  <si>
+    <t>P.S. LACHCHIPUR MO RAMAPURKALA</t>
+  </si>
+  <si>
+    <t>J.H.S. RAMAPURKALA KAMRA NO 1</t>
+  </si>
+  <si>
+    <t>J.H.S. RAMAPURKALA KAMRA NO 2</t>
+  </si>
+  <si>
+    <t>PANCHYATGHAR BANBEERPUR MO RAMAPURKALA</t>
+  </si>
+  <si>
+    <t>P.S. MAJHIYA KAMRA NO 1</t>
+  </si>
+  <si>
+    <t>P.S. MAJHIYA KAMRA NO 2</t>
+  </si>
+  <si>
+    <t>P.S. SARAIYASHANKAR BAKSH</t>
+  </si>
+  <si>
+    <t>P.S. SANDAUR</t>
+  </si>
+  <si>
+    <t>P.S. DUDHRA KAMRA NO 1</t>
+  </si>
+  <si>
+    <t>P.S. LAKHAVAPUR MO BERASAPUR</t>
+  </si>
+  <si>
+    <t>P.S. MAVAIYA</t>
+  </si>
+  <si>
+    <t>P.S. CHAUDIYABHAJJUPUR</t>
+  </si>
+  <si>
+    <t>P.S. PIPRA MO BAHATUTAPUR</t>
+  </si>
+  <si>
+    <t>P.S. SEMRA</t>
+  </si>
+  <si>
+    <t>P.S.TEWARIPUR MO DAHAIYA KAMRA NO 1</t>
+  </si>
+  <si>
+    <t>P.S.TEWARIPUR MO DAHAIYA KAMRA NO 2</t>
+  </si>
+  <si>
+    <t>P.S. DAHAVA PURAB KAMRA</t>
+  </si>
+  <si>
+    <t>P.S.DAHAVA PASHIM KAMRA</t>
+  </si>
+  <si>
+    <t>P.S. BARETHI</t>
+  </si>
+  <si>
+    <t>P.S. SANDHANA KAMRA NO 1</t>
+  </si>
+  <si>
+    <t>P.S. SANDHANA KAMRA NO 2</t>
+  </si>
+  <si>
+    <t>P.S. CHHANJAN</t>
+  </si>
+  <si>
+    <t>P.S. SITARASOI UATTARI KAMRA</t>
+  </si>
+  <si>
+    <t>P.S. SITARASOI MADHY KAMRA</t>
+  </si>
+  <si>
+    <t>P.S. SONARI M0 SITARASOI KAMRA NO 1</t>
+  </si>
+  <si>
+    <t>P.S. SONARI M0 SITARASOI KAMRA NO 2</t>
+  </si>
+  <si>
+    <t>P.S. VISHUNADASAPUR</t>
+  </si>
+  <si>
+    <t>P.S. KANHAMAU KAMRA NO 1</t>
+  </si>
+  <si>
+    <t>P.S. KANHAMAU KAMRA NO 2</t>
+  </si>
+  <si>
+    <t>P.S. HANUMANAPUR</t>
+  </si>
+  <si>
+    <t>P.S. MAANAPARA</t>
+  </si>
+  <si>
+    <t>P.S. CHAUDIYA M0 MAANAPARA</t>
+  </si>
+  <si>
+    <t>P.S. PURNAPUR</t>
+  </si>
+  <si>
+    <t>J.H.S. HIRAPUR</t>
+  </si>
+  <si>
+    <t>P.S. SINGHAPUR</t>
+  </si>
+  <si>
+    <t>P.S. PAISIYA</t>
+  </si>
+  <si>
+    <t>P.S. KINDHAULIYA</t>
+  </si>
+  <si>
+    <t>P.S. REURI KAMRA NO 1</t>
+  </si>
+  <si>
+    <t>P.S. REVRI KAMRA NO 2</t>
+  </si>
+  <si>
+    <t>P.S.MEHADAULI</t>
+  </si>
+  <si>
+    <t>J.H.S. BASAIDIH KAMRA NO 1</t>
+  </si>
+  <si>
+    <t>J.H.S. BASAIDIH KAMRA NO 2</t>
+  </si>
+  <si>
+    <t>P.S. THITHURA M0 BASAIDIH</t>
+  </si>
+  <si>
+    <t>P.S. JATHA</t>
+  </si>
+  <si>
+    <t>P.S. DHAKHA</t>
+  </si>
+  <si>
+    <t>P.S. NAHOIYA</t>
+  </si>
+  <si>
+    <t>P.S. KUCHILAI</t>
+  </si>
+  <si>
+    <t>SANKUL BHAVAN KUCHILAI</t>
+  </si>
+  <si>
+    <t>P.S. GANGOY</t>
+  </si>
+  <si>
+    <t>P.S. ASAL KAMRA NO 1</t>
+  </si>
+  <si>
+    <t>P.S. ASAL KAMRA NO 2</t>
+  </si>
+  <si>
+    <t>P.S. GADHVAI</t>
+  </si>
+  <si>
+    <t>P.S. BAROY</t>
+  </si>
+  <si>
+    <t>P.S. BHARAUNA</t>
+  </si>
+  <si>
+    <t>P.S. BISAULI</t>
+  </si>
+  <si>
+    <t>P.S. PAKRANARAYNAPUR</t>
+  </si>
+  <si>
+    <t>P.S. KAMALAPUR</t>
+  </si>
+  <si>
+    <t>P.S. GOVINDAPUR</t>
+  </si>
+  <si>
+    <t>P.S. TARAPUR</t>
+  </si>
+  <si>
+    <t>SRI DHRAVAL DEVI VIDHYA MINDIR J.H.S.DHARAULI KAMRA NO 1</t>
+  </si>
+  <si>
+    <t>SRI DHRAVAL DEVI VIDHYA MINDIR J.H.S.DHARAULI KAMRA NO 2</t>
+  </si>
+  <si>
+    <t>P.S. NAYI GANDHI M0 DHARAULI</t>
+  </si>
+  <si>
+    <t>P.S . CHAUPARIYA</t>
+  </si>
+  <si>
+    <t>P.S. ASUVAMAU UATTAR KAMRA</t>
+  </si>
+  <si>
+    <t>P.S ASUVAMAU DAKSHIN KAMRA</t>
+  </si>
+  <si>
+    <t>P.S JOHARIYAMAU</t>
+  </si>
+  <si>
+    <t>P.S GONDALAMAU KAMRA NO 1</t>
+  </si>
+  <si>
+    <t>P.S GONDALAMAU KAMRA NO 2</t>
+  </si>
+  <si>
+    <t>P.S PATTI NEVADA</t>
+  </si>
+  <si>
+    <t>P.S GANGUPUR KAMRA NO 1</t>
+  </si>
+  <si>
+    <t>P.S RAMNAGAR M0 GANGUPUR</t>
+  </si>
+  <si>
+    <t>J.H.S. KUNVARAPUR</t>
+  </si>
+  <si>
+    <t>P.S MAHESHAPUR</t>
+  </si>
+  <si>
+    <t>P.S TERVA KAMRA NO 1</t>
+  </si>
+  <si>
+    <t>P.S TERVA KAMRA NO 2</t>
+  </si>
+  <si>
+    <t>P.S. SHIVAPURI</t>
+  </si>
+  <si>
+    <t>J.H.S. KHERVA</t>
+  </si>
+  <si>
+    <t>P.S. GAURIYA KAMRA NO 1</t>
+  </si>
+  <si>
+    <t>P.S. GAURIYA KAMRA NO 2</t>
+  </si>
+  <si>
+    <t>P.S. NARAYNAPUR</t>
+  </si>
+  <si>
+    <t>P.S. GAITHA</t>
+  </si>
+  <si>
+    <t>P.S. KABIRAPUR</t>
+  </si>
+  <si>
+    <t>P.S. TAUKLAPUR</t>
+  </si>
+  <si>
+    <t>P.S. MUDIYAKAIL</t>
+  </si>
+  <si>
+    <t>P.S. SARAIYA</t>
+  </si>
+  <si>
+    <t>P.S. DEVRI KAIL</t>
+  </si>
+  <si>
+    <t>P.S. MAHMDPUR JHAB</t>
+  </si>
+  <si>
+    <t>P.S. RASULAPUR</t>
+  </si>
+  <si>
+    <t>P.S. PARA</t>
+  </si>
+  <si>
+    <t>P.S. UMEDAPUR M0 /PARA</t>
+  </si>
+  <si>
+    <t>J.H.S. ISMAILGANJ KAMRA NO 1</t>
+  </si>
+  <si>
+    <t>J.H.S. ISMAIL GANJ KAMRA NO 2</t>
+  </si>
+  <si>
+    <t>P.S. KHALEGDHI</t>
+  </si>
+  <si>
+    <t>P.S. KOTHAVAN</t>
+  </si>
+  <si>
+    <t>P.S. GANESHAPUR M0 KOTHAVAN</t>
+  </si>
+  <si>
+    <t>P.S. LOHANGAPUR</t>
+  </si>
+  <si>
+    <t>P.S. NANDAVAN</t>
+  </si>
+  <si>
+    <t>P.S. GADHIKHERVA</t>
+  </si>
+  <si>
+    <t>P.S. GOPALAPUR PURVI KAMRA NO 1</t>
+  </si>
+  <si>
+    <t>P.S. GOPALAPUR PURVI KAMRA NO 2</t>
+  </si>
+  <si>
+    <t>K.P.S. SAHOLI PURAB KAMRA</t>
+  </si>
+  <si>
+    <t>K.P.S. SAHOLI PASHIM KAMRA</t>
+  </si>
+  <si>
+    <t>P.S. KURSI KAMRA NO 1</t>
+  </si>
+  <si>
+    <t>P.S. KURSI KAMRA NO 2</t>
+  </si>
+  <si>
+    <t>J.S.H. ALLIPUR KAMRA NO 1</t>
+  </si>
+  <si>
+    <t>J.H.S. ALLIPUR KAMRA NO 2</t>
+  </si>
+  <si>
+    <t>SRI GOMTESHWAR JHS KAMRA NO 1 HINDAURA</t>
+  </si>
+  <si>
+    <t>SRI GOMTESHWAR JHS KAMRA NO 2</t>
+  </si>
+  <si>
+    <t>P.S. BHAGAVANAPUR M0 HINDAURA</t>
+  </si>
+  <si>
+    <t>P.S. NAYA BHAVAN MOHADDINAPUR</t>
+  </si>
+  <si>
+    <t>P.S. BALAPUR</t>
+  </si>
+  <si>
+    <t>P.S. BHIKHAPUR</t>
+  </si>
+  <si>
+    <t>P.S. CHANDAPUR</t>
+  </si>
+  <si>
+    <t>J.H.S. BADI KAMRA NO 1</t>
+  </si>
+  <si>
+    <t>J.H.S. BADI KAMRA NO 2</t>
+  </si>
+  <si>
+    <t>J.H.S. BADI KAMRA NO 3</t>
+  </si>
+  <si>
+    <t>BLOCK SANSADHAN KENDRA BADI</t>
+  </si>
+  <si>
+    <t>P.S. BADI KAMRA NO 1</t>
+  </si>
+  <si>
+    <t>P.S. BADI KAMRA NO 2</t>
+  </si>
+  <si>
+    <t>P.S. ALADADAPUR KAMRA NO 1</t>
+  </si>
+  <si>
+    <t>P.S. ALADADAPUR KAMRA NO 2</t>
+  </si>
+  <si>
+    <t>G.V.I.C.SIDHAULI KAMRA NO 2</t>
+  </si>
+  <si>
+    <t>G.V.I.C.SIDHAULI KAMRA NO 3</t>
+  </si>
+  <si>
+    <t>G.V.I.C. SIDHAULI KAMRA NO 11</t>
+  </si>
+  <si>
+    <t>K.V.I.C.SIDHAULI KAMRA NO 1</t>
+  </si>
+  <si>
+    <t>K.V.I.C.SIDHAULI KAMRA NO 2</t>
+  </si>
+  <si>
+    <t>K.V.I.C.SIDHAULI KAMRA NO 3</t>
+  </si>
+  <si>
+    <t>DI.SI.H.S.S.SIDHAULI KAMRA NO 1</t>
+  </si>
+  <si>
+    <t>DI.SI.H.S.S. SIDHAULI KAMRA NO 2</t>
+  </si>
+  <si>
+    <t>DI.SI.H.S.S. SIDHAULI KAMRA NO 3</t>
+  </si>
+  <si>
+    <t>NE.VI.JHS SIDHAULI KAMRA NO 1</t>
+  </si>
+  <si>
+    <t>NE.VI.JHS SIDHAULI KAMRA NO 2</t>
+  </si>
+  <si>
+    <t>NE.VI.JHS SIDHAULI KAMRA NO 3</t>
+  </si>
+  <si>
+    <t>P.S. NAROTTAM NAGAR NIKAT DAK BANGLA SIDHAULI KAMRA NO 1</t>
+  </si>
+  <si>
+    <t>P.S. NAROTTAM NAGAR NIKAT DAK BANGLA SIDHAULI KAMRA NO 2</t>
+  </si>
+  <si>
+    <t>P.S. NAROTTAM NAGAR NIKAT DAK BANGLA SIDHAULI KAMRA NO 3</t>
+  </si>
+  <si>
+    <t>P.S. NAYA BHAVAN NAROTTAM NAGAR NIKAT DAK BANGLA</t>
+  </si>
+  <si>
+    <t>P.S. NAYA BHAVAN NAROTTAM NAGAR NIKAT DAK BANGLA SIDHAULI KAMRA NO 2</t>
+  </si>
+  <si>
+    <t>J.H.S. AHAMDAPUR JAT KAMRA NO 1</t>
+  </si>
+  <si>
+    <t>J.H.S. AHAMDAPUR JAT KAMRA NO 2</t>
+  </si>
+  <si>
+    <t>P.S. GADIYA HASNAPUR KAMRA NO 1</t>
+  </si>
+  <si>
+    <t>P.S. GADIYA HASNAPUR KAMRA NO 2</t>
+  </si>
+  <si>
+    <t>P.S. MURAHADIH</t>
+  </si>
+  <si>
+    <t>P.S. KAJIKOLA</t>
+  </si>
+  <si>
+    <t>P.S. FIROJAPUR</t>
+  </si>
+  <si>
+    <t>P.S. GANIPUR</t>
+  </si>
+  <si>
+    <t>P.S. AKOHARA</t>
+  </si>
+  <si>
+    <t>P.S. SARASAULI</t>
+  </si>
+  <si>
+    <t>P.S. MUKIMAPUR</t>
+  </si>
+  <si>
+    <t>P.S. JODNAURA KAMRA NO 1</t>
+  </si>
+  <si>
+    <t>P.S. JODNAURA KAMRA NO 2</t>
+  </si>
+  <si>
+    <t>P.S. TADAIKLA KAMRA NO 1</t>
+  </si>
+  <si>
+    <t>P.S. TADAIKLA KAMRA NO 2</t>
+  </si>
+  <si>
+    <t>P.S. BIBIPUR</t>
+  </si>
+  <si>
+    <t>P.S. TADAIKHURD</t>
+  </si>
+  <si>
+    <t>P.S. KASHIPUR</t>
+  </si>
+  <si>
+    <t>P.S. BAHADURAPUR</t>
+  </si>
+  <si>
+    <t>P.S. HUSENGANJ UATTARI KAMRA</t>
+  </si>
+  <si>
+    <t>P.S. HUSENGANJ DAKSHINI KAMRA</t>
+  </si>
+  <si>
+    <t>P.S. JHAKHARANVA</t>
+  </si>
+  <si>
+    <t>P.S. BANIYANI</t>
+  </si>
+  <si>
+    <t>P.S. HARADOIYA</t>
+  </si>
+  <si>
+    <t>P.S. SARVA MO HARADOIYA KAMRA NO 1</t>
+  </si>
+  <si>
+    <t>P.S. SARVA MO HARADOIYA KAMRA NO 2</t>
+  </si>
+  <si>
+    <t>P.S. SEERGANG MO BHITHAURA</t>
+  </si>
+  <si>
+    <t>PANCHAYATGHAR KATSARAIYA</t>
+  </si>
+  <si>
+    <t>J.H.S. KHARVALIYA KAMRA NO 1</t>
+  </si>
+  <si>
+    <t>J.H.S. KHARVALIYA KAMRA NO 2</t>
+  </si>
+  <si>
+    <t>P.S. RAMADANA</t>
+  </si>
+  <si>
+    <t>J.H.S. BAHERVA</t>
+  </si>
+  <si>
+    <t>J.H.S. UNCHAKHERAAJAI</t>
+  </si>
+  <si>
+    <t>P.S. UNCHAKHERAAJAI</t>
+  </si>
+  <si>
+    <t>K.P.S. BHANDIYA</t>
+  </si>
+  <si>
+    <t>SANKUL BHAWAN BHANDIYA</t>
+  </si>
+  <si>
+    <t>P.S. PRATHAM BHANDIYA KAMRA NO</t>
+  </si>
+  <si>
+    <t>P.S. REHUVA</t>
+  </si>
+  <si>
+    <t>P.S. CHAUDIYA</t>
+  </si>
+  <si>
+    <t>P.S. JALALPUR</t>
+  </si>
+  <si>
+    <t>P.S. KHAIRANDESH NAGAR</t>
+  </si>
+  <si>
+    <t>P.S. KABRA</t>
+  </si>
+  <si>
+    <t>P.S. DALAMAU</t>
+  </si>
+  <si>
+    <t>P.S. DIKAULI</t>
+  </si>
+  <si>
+    <t>P.S. PARVAR BHARI</t>
+  </si>
+  <si>
+    <t>PANCHAYATGHAR SURJANAPUR</t>
+  </si>
+  <si>
+    <t>P.S. MADURI MO DILLI AGRA</t>
+  </si>
+  <si>
+    <t>P.S. RAMAPUR BHUJANG</t>
+  </si>
+  <si>
+    <t>P.S. MOHABBATAPUR</t>
+  </si>
+  <si>
+    <t>P.S. KANDAURA</t>
+  </si>
+  <si>
+    <t>P.S. BEHAMA KAMRA NO 1</t>
+  </si>
+  <si>
+    <t>P.S. BEHAMA KAMRA NO 2</t>
+  </si>
+  <si>
+    <t>P.S. NAVAGANVA</t>
+  </si>
+  <si>
+    <t>P.S.KANCHANPUR MO KHERIYA</t>
+  </si>
+  <si>
+    <t>P.S. DULARAPUR</t>
+  </si>
+  <si>
+    <t>P.S. MADILA MO ALOIYA</t>
+  </si>
+  <si>
+    <t>P.S. BALOIYA KAMRA NO 1</t>
+  </si>
+  <si>
+    <t>P.S. BALOIYA KAMRA NO 2</t>
+  </si>
+  <si>
+    <t>P.S. RAMNAGRA</t>
+  </si>
+  <si>
+    <t>P.S. KUNWARGADDI M0 MAGARAURA KAMRA NO 1</t>
+  </si>
+  <si>
+    <t>P.S. KUNWARGADDI M0 MAGARAURA KAMRA NO 2</t>
+  </si>
+  <si>
+    <t>P.S. MANPUR M0 ASODHAN KAMRA NO 1</t>
+  </si>
+  <si>
+    <t>SANKUL BHAWAN MANPUR M0 ASODHAN</t>
+  </si>
+  <si>
+    <t>P.S.AHAMDAPUR DHAKHVA</t>
+  </si>
+  <si>
+    <t>P.S. HARAIYA KAMRA NO 1</t>
+  </si>
+  <si>
+    <t>P.S. HARAIYA KAMRA NO 2</t>
+  </si>
+  <si>
+    <t>P.S. BILARIYA UATTAR KAMRA</t>
+  </si>
+  <si>
+    <t>P.S. BILARIYA DAKSHIN KAMRA</t>
+  </si>
+  <si>
+    <t>P.S. SHAHAJAHAMPUR</t>
+  </si>
+  <si>
+    <t>P.S. ASENIYA M0 SHAHAJAHAMPUR</t>
+  </si>
+  <si>
+    <t>P.S. PANDENRAMAPUR M0 SHAHAJAHAMPUR</t>
+  </si>
+  <si>
+    <t>P.S. KHAJURIYA</t>
+  </si>
+  <si>
+    <t>P.S. KUTI M0 GAJIPUR</t>
+  </si>
+  <si>
+    <t>P.S. GANDHAULI PURABI KAMRA</t>
+  </si>
+  <si>
+    <t>P.S. GANDHAULI PASHIMI KAMRA</t>
+  </si>
+  <si>
+    <t>P.S. UMRA KAMRA NO 1</t>
+  </si>
+  <si>
+    <t>P.S. UMRA KAMRA NO 2</t>
+  </si>
+  <si>
+    <t>J.H.S.BAUNA BHARI PURABI KAMRA</t>
+  </si>
+  <si>
+    <t>J.H.S.BAUNA BHARI PASCHIMI KAMRA</t>
+  </si>
+  <si>
+    <t>P.S. ALBADA</t>
+  </si>
+  <si>
+    <t>P.S. MUJAPFARAPUR</t>
+  </si>
+  <si>
+    <t>P.S. MANIKAPUR</t>
+  </si>
+  <si>
+    <t>P.S. JALLABAD</t>
+  </si>
+  <si>
+    <t>P.S. SARAVANIKTABADI</t>
+  </si>
+  <si>
+    <t>P.S. KIRATAPUR</t>
+  </si>
+  <si>
+    <t>P.S. GADHIRAVAN</t>
+  </si>
+  <si>
+    <t>P.S. NAVIN MANVA KAMRA NO 1</t>
+  </si>
+  <si>
+    <t>P.S. NAVIN MANVA KAMRA NO 2</t>
+  </si>
+  <si>
+    <t>P.S. ALAMAPUR</t>
+  </si>
+  <si>
+    <t>P.S. JAJAUR KAMRA NO 1</t>
+  </si>
+  <si>
+    <t>P.S. JAJAUR KAMRA NO 2</t>
+  </si>
+  <si>
+    <t>P.S. KANTAIN</t>
+  </si>
+  <si>
+    <t>P.S. AMBARAPUR KAMRA NO 1</t>
+  </si>
+  <si>
+    <t>P.S. AMBARAPUR KAMRA NO 2</t>
+  </si>
+  <si>
+    <t>P.S. BERASAPUR</t>
+  </si>
+  <si>
+    <t>P.S. GULRIHA</t>
+  </si>
+  <si>
+    <t>P.S. MADANAPUR MO GULRIHA</t>
+  </si>
+  <si>
+    <t>P.S. RANUVAPARA</t>
+  </si>
+  <si>
+    <t>P.S. HIRAPUR</t>
+  </si>
+  <si>
+    <t>P.S. MAU</t>
+  </si>
+  <si>
+    <t>P.S. GODHNA KAMRA NO 1</t>
+  </si>
+  <si>
+    <t>P.S. GODHNA KAMRA NO 2</t>
+  </si>
+  <si>
+    <t>J.H.S. BAKHATKHERA M0 GODHNA</t>
+  </si>
+  <si>
+    <t>P.S. BHATKHERWA M0 SAHAJNAPUR</t>
+  </si>
+  <si>
+    <t>P.S. TIKAULI KAMRA NO 1</t>
+  </si>
+  <si>
+    <t>P.S. TIKAULI KAMRA NO 2</t>
+  </si>
+  <si>
+    <t>P.S. PIRATHIPUR</t>
+  </si>
+  <si>
+    <t>P.S. PASHCHIMAGANVA</t>
+  </si>
+  <si>
+    <t>P.S. SARAURA KAMRA NO 1</t>
+  </si>
+  <si>
+    <t>P.S. SARAURA KAMRA NO 2</t>
+  </si>
+  <si>
+    <t>P.S. TEDVA MO RAMAPUR TEDVA</t>
+  </si>
+  <si>
+    <t>P.S. RAMAPUR TEDVA</t>
+  </si>
+  <si>
+    <t>P.S. UNAI KAMRA NO 1</t>
+  </si>
+  <si>
+    <t>P.S. UNAI KAMRA NO 2</t>
+  </si>
+  <si>
+    <t>J.H.S. AKBARAPUR UNAI</t>
+  </si>
+  <si>
+    <t>P.S. RAMNAGRA M0 AKBARAPUR</t>
+  </si>
+  <si>
+    <t>P.S. MISNI</t>
+  </si>
+  <si>
+    <t>P.S. PRTHAM RAMNAGRA MO BANSAKHERA</t>
+  </si>
+  <si>
+    <t>P.S. DUTEEY BANSAKHERA</t>
+  </si>
+  <si>
+    <t>R.I.C. NILAGANVA KAMRA NO 1</t>
+  </si>
+  <si>
+    <t>R.I.C. NILAGANVA KAMRA NO 2</t>
+  </si>
+  <si>
+    <t>R.I.C. NILAGANVA KAMRA NO 3</t>
+  </si>
+  <si>
+    <t>P.S. GRANT MO. DHARANGAR</t>
+  </si>
+  <si>
+    <t>P.S. JANAKINGAR M0 PAHADAPUR</t>
+  </si>
+  <si>
+    <t>J.H.S. PAHADAPUR</t>
+  </si>
+  <si>
+    <t>P.S. DAKHINANVA</t>
+  </si>
+  <si>
+    <t>P.S. MADRIPUR MO. AHEVA KAMRA NO 1</t>
+  </si>
+  <si>
+    <t>P.S. MADRIPUR MO. AHEVA KAMRA NO 2</t>
+  </si>
+  <si>
+    <t>P.S.GANERA</t>
+  </si>
+  <si>
+    <t>P.S. HIMMATNAGAR</t>
+  </si>
+  <si>
+    <t>P.S. CHHAVAN</t>
+  </si>
+  <si>
+    <t>P.S. KATHVA</t>
+  </si>
+  <si>
+    <t>P.S. ALAIPUR</t>
+  </si>
+  <si>
+    <t>P.S. SASENA</t>
+  </si>
+  <si>
+    <t>P.S. ANVARAPUR</t>
+  </si>
+  <si>
+    <t>P.S. PAREVAJAL PURBI KAMRA</t>
+  </si>
+  <si>
+    <t>P.S. PAREVAJAL PASCHIMI KAMRA</t>
+  </si>
+  <si>
+    <t>K.J.H.S.PANPUR MO KASANVA</t>
+  </si>
+  <si>
+    <t>P.S KASANVA</t>
+  </si>
+  <si>
+    <t>P.S. BAHADURAPUR MO KASANVA</t>
+  </si>
+  <si>
+    <t>K.J.H.S. ATARIYA KAMRA NO1</t>
+  </si>
+  <si>
+    <t>K.J.H.S. ATARIYA KAMRA NO2</t>
+  </si>
+  <si>
+    <t>K.J.H.S. ATARIYA KAMRA NO3</t>
+  </si>
+  <si>
+    <t>P.S. BANAUGA</t>
+  </si>
+  <si>
+    <t>J.H.S. DHARANVA</t>
+  </si>
+  <si>
+    <t>P.S. HAMIRAPUR</t>
+  </si>
+  <si>
+    <t>P.S. AKBARAPUR REVAN KAMRA NO 1</t>
+  </si>
+  <si>
+    <t>P.S. AKBARAPUR REVAN KAMRA NO 2</t>
+  </si>
+  <si>
+    <t>P.S.SARANYA</t>
+  </si>
+  <si>
+    <t>P.S. LAHUREVAN</t>
+  </si>
+  <si>
+    <t>P.S. SALEMAPUR</t>
+  </si>
+  <si>
+    <t>P.S. BIRASINGHAPUR</t>
+  </si>
+  <si>
+    <t>P.S. RAYAPUR DEVASINGH</t>
+  </si>
+  <si>
+    <t>P.S. NAVAGANVA KAMRA NO 1</t>
+  </si>
+  <si>
+    <t>P.S. NAVAGANVA KAMRA NO 2</t>
+  </si>
+  <si>
+    <t>P.S KHANIPUR MO NAVAGANVA</t>
+  </si>
+  <si>
+    <t>P.S. DUNDAPUR</t>
+  </si>
+  <si>
+    <t>P.S RIWANKALA KAMRA NO 1</t>
+  </si>
+  <si>
+    <t>P.S. RIWANKALA KAMRA NO 2</t>
+  </si>
+  <si>
+    <t>J.M.V. KUVRAPUR KAMRA NO1</t>
+  </si>
+  <si>
+    <t>J.M.V. KUVRAPUR KAMRA NO2</t>
+  </si>
+  <si>
+    <t>P.S. JAYAPALAPUR KAMRA NO 1</t>
+  </si>
+  <si>
+    <t>P.S. JAYAPALAPUR KAMRA NO 2</t>
+  </si>
+  <si>
+    <t>P.S. CHANDESUVA</t>
+  </si>
+  <si>
+    <t>J.H.S.KODARIYA KAMRA NO 1</t>
+  </si>
+  <si>
+    <t>J.H.S.KODARIYA KAMRA NO 2</t>
+  </si>
+  <si>
+    <t>P.S. GULALPUR MO KODARIYA</t>
+  </si>
+  <si>
+    <t>P.S. RAYAPUR KUNVARAPUR</t>
+  </si>
+  <si>
+    <t>P.S. AITHAPUR MO DAKKHIN GANVA</t>
+  </si>
+  <si>
+    <t>P.S. BHANAPUR</t>
+  </si>
+  <si>
+    <t>P.S. BHANAPUR ROOM NO. 362</t>
+  </si>
+  <si>
+    <t>P.S. BHANAPUR ROOM ROOM NO. 363</t>
+  </si>
+  <si>
+    <t>P.S. BHANAPUR ROOM ROOM ROOM NO. 364</t>
+  </si>
+  <si>
+    <t>P.S. BHANAPUR ROOM ROOM ROOM ROOM NO. 365</t>
+  </si>
+  <si>
+    <t>P.S. BHANAPUR ROOM ROOM ROOM ROOM ROOM NO. 366</t>
+  </si>
+  <si>
+    <t>P.S. BHANAPUR ROOM ROOM ROOM ROOM ROOM ROOM NO. 367</t>
+  </si>
+  <si>
+    <t>P.S. BHANAPUR ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 368</t>
+  </si>
+  <si>
+    <t>P.S. BHANAPUR ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 369</t>
+  </si>
+  <si>
+    <t>P.S. BHANAPUR ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 370</t>
+  </si>
+  <si>
+    <t>P.S. BHANAPUR ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 371</t>
+  </si>
+  <si>
+    <t>P.S. BHANAPUR ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 372</t>
+  </si>
+  <si>
+    <t>P.S. BHANAPUR ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 373</t>
+  </si>
+  <si>
+    <t>P.S. BHANAPUR ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 374</t>
+  </si>
+  <si>
+    <t>P.S. BHANAPUR ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 375</t>
+  </si>
+  <si>
+    <t>P.S. BHANAPUR ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 376</t>
+  </si>
+  <si>
+    <t>P.S. BHANAPUR ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 377</t>
+  </si>
+  <si>
+    <t>P.S. BHANAPUR ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 378</t>
+  </si>
+  <si>
+    <t>P.S. BHANAPUR ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 379</t>
+  </si>
+  <si>
+    <t>P.S. BHANAPUR ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 380</t>
+  </si>
+  <si>
+    <t>P.S. BHANAPUR ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 381</t>
+  </si>
+  <si>
+    <t>P.S. BHANAPUR ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 382</t>
+  </si>
+  <si>
+    <t>P.S. BHANAPUR ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 383</t>
+  </si>
+  <si>
+    <t>P.S. BHANAPUR ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 384</t>
+  </si>
+  <si>
+    <t>P.S. BHANAPUR ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 385</t>
+  </si>
+  <si>
+    <t>P.S. BHANAPUR ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 386</t>
+  </si>
+  <si>
+    <t>P.S. BHANAPUR ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 387</t>
+  </si>
+  <si>
+    <t>P.S. BHANAPUR ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 388</t>
+  </si>
+  <si>
+    <t>P.S. BHANAPUR ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 389</t>
+  </si>
+  <si>
+    <t>P.S. BHANAPUR ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 390</t>
+  </si>
+  <si>
+    <t>P.S. BHANAPUR ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 391</t>
+  </si>
+  <si>
+    <t>P.S. BHANAPUR ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 392</t>
+  </si>
+  <si>
+    <t>P.S. BHANAPUR ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 393</t>
+  </si>
+  <si>
+    <t>P.S. BHANAPUR ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 394</t>
+  </si>
+  <si>
+    <t>P.S. BHANAPUR ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 395</t>
+  </si>
+  <si>
+    <t>P.S. BHANAPUR ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 396</t>
+  </si>
+  <si>
+    <t>P.S. BHANAPUR ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 397</t>
+  </si>
+  <si>
+    <t>P.S. BHANAPUR ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 398</t>
+  </si>
+  <si>
+    <t>P.S. BHANAPUR ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 399</t>
+  </si>
+  <si>
+    <t>P.S. BHANAPUR ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 400</t>
+  </si>
+  <si>
+    <t>P.S. BHANAPUR ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 401</t>
+  </si>
+  <si>
+    <t>P.S. BHANAPUR ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 402</t>
+  </si>
+  <si>
+    <t>P.S. BHANAPUR ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 403</t>
+  </si>
+  <si>
+    <t>P.S. BHANAPUR ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 404</t>
+  </si>
+  <si>
+    <t>P.S. BHANAPUR ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 405</t>
+  </si>
+  <si>
+    <t>P.S. BHANAPUR ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 406</t>
+  </si>
+  <si>
+    <t>P.S. BHANAPUR ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 407</t>
+  </si>
+  <si>
+    <t>P.S. BHANAPUR ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 408</t>
+  </si>
+  <si>
+    <t>P.S. BHANAPUR ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 409</t>
+  </si>
+  <si>
+    <t>P.S. BHANAPUR ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 410</t>
+  </si>
+  <si>
+    <t>P.S. BHANAPUR ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 411</t>
+  </si>
+  <si>
+    <t>P.S. BHANAPUR ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 412</t>
+  </si>
+  <si>
+    <t>P.S. BHANAPUR ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 413</t>
+  </si>
+  <si>
+    <t>P.S. BHANAPUR ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 414</t>
+  </si>
+  <si>
+    <t>P.S. BHANAPUR ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 415</t>
+  </si>
+  <si>
+    <t>P.S. BHANAPUR ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 416</t>
+  </si>
+  <si>
+    <t>P.S. BHANAPUR ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 417</t>
+  </si>
+  <si>
+    <t>P.S. BHANAPUR ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 418</t>
+  </si>
+  <si>
+    <t>P.S. BHANAPUR ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 419</t>
+  </si>
+  <si>
+    <t>P.S. BHANAPUR ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 420</t>
+  </si>
+  <si>
+    <t>P.S. BHANAPUR ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 421</t>
+  </si>
+  <si>
+    <t>P.S. BHANAPUR ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 422</t>
+  </si>
+  <si>
+    <t>P.S. BHANAPUR ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 423</t>
+  </si>
+  <si>
+    <t>P.S. BHANAPUR ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 424</t>
+  </si>
+  <si>
+    <t>P.S. BHANAPUR ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 425</t>
+  </si>
+  <si>
+    <t>P.S. BHANAPUR ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 426</t>
+  </si>
+  <si>
+    <t>P.S. BHANAPUR ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 427</t>
   </si>
   <si>
     <t>TOTAL ELECTORS</t>
@@ -797,8 +1451,16 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="1">
+  <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -814,7 +1476,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -822,12 +1484,30 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1126,88 +1806,163 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:26">
-      <c r="A1" t="s">
-        <v>0</v>
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z1" s="1" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="2" spans="1:26">
       <c r="A2" t="s">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="B2" t="s">
-        <v>2</v>
+        <v>27</v>
       </c>
       <c r="C2" t="s">
-        <v>236</v>
+        <v>454</v>
       </c>
       <c r="D2" t="s">
-        <v>237</v>
+        <v>455</v>
       </c>
       <c r="E2" t="s">
-        <v>238</v>
+        <v>456</v>
       </c>
       <c r="F2" t="s">
-        <v>239</v>
+        <v>457</v>
       </c>
       <c r="G2" t="s">
-        <v>240</v>
+        <v>458</v>
       </c>
       <c r="H2" t="s">
-        <v>241</v>
+        <v>459</v>
       </c>
       <c r="I2" t="s">
-        <v>242</v>
+        <v>460</v>
       </c>
       <c r="J2" t="s">
-        <v>243</v>
+        <v>461</v>
       </c>
       <c r="K2" t="s">
-        <v>244</v>
+        <v>462</v>
       </c>
       <c r="L2" t="s">
-        <v>245</v>
+        <v>463</v>
       </c>
       <c r="M2" t="s">
-        <v>246</v>
+        <v>464</v>
       </c>
       <c r="N2" t="s">
-        <v>247</v>
+        <v>465</v>
       </c>
       <c r="O2" t="s">
-        <v>248</v>
+        <v>466</v>
       </c>
       <c r="P2" t="s">
-        <v>249</v>
+        <v>467</v>
       </c>
       <c r="Q2" t="s">
-        <v>250</v>
+        <v>468</v>
       </c>
       <c r="R2" t="s">
-        <v>251</v>
+        <v>469</v>
       </c>
       <c r="S2" t="s">
-        <v>252</v>
+        <v>470</v>
       </c>
       <c r="T2" t="s">
-        <v>253</v>
+        <v>471</v>
       </c>
       <c r="U2" t="s">
-        <v>254</v>
+        <v>472</v>
       </c>
       <c r="V2" t="s">
-        <v>255</v>
+        <v>473</v>
       </c>
       <c r="W2" t="s">
-        <v>256</v>
+        <v>474</v>
       </c>
       <c r="X2" t="s">
-        <v>256</v>
+        <v>474</v>
       </c>
       <c r="Y2" t="s">
-        <v>257</v>
+        <v>475</v>
       </c>
       <c r="Z2" t="s">
-        <v>258</v>
+        <v>476</v>
       </c>
     </row>
     <row r="3" spans="1:26">
@@ -1215,7 +1970,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>3</v>
+        <v>28</v>
       </c>
       <c r="C3">
         <v>602</v>
@@ -1295,7 +2050,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>4</v>
+        <v>29</v>
       </c>
       <c r="C4">
         <v>900</v>
@@ -1375,7 +2130,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="C5">
         <v>383</v>
@@ -1455,7 +2210,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>6</v>
+        <v>31</v>
       </c>
       <c r="C6">
         <v>666</v>
@@ -1535,7 +2290,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>7</v>
+        <v>32</v>
       </c>
       <c r="C7">
         <v>1077</v>
@@ -1615,7 +2370,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>8</v>
+        <v>33</v>
       </c>
       <c r="C8">
         <v>654</v>
@@ -1695,7 +2450,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="C9">
         <v>991</v>
@@ -1775,7 +2530,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="C10">
         <v>566</v>
@@ -1855,7 +2610,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>11</v>
+        <v>36</v>
       </c>
       <c r="C11">
         <v>1048</v>
@@ -1935,7 +2690,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>12</v>
+        <v>37</v>
       </c>
       <c r="C12">
         <v>1045</v>
@@ -2015,7 +2770,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>11</v>
+        <v>38</v>
       </c>
       <c r="C13">
         <v>486</v>
@@ -2095,7 +2850,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="C14">
         <v>1025</v>
@@ -2175,7 +2930,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="C15">
         <v>1088</v>
@@ -2255,7 +3010,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>7</v>
+        <v>41</v>
       </c>
       <c r="C16">
         <v>936</v>
@@ -2335,7 +3090,7 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>15</v>
+        <v>42</v>
       </c>
       <c r="C17">
         <v>714</v>
@@ -2415,7 +3170,7 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>7</v>
+        <v>43</v>
       </c>
       <c r="C18">
         <v>805</v>
@@ -2495,7 +3250,7 @@
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>16</v>
+        <v>44</v>
       </c>
       <c r="C19">
         <v>377</v>
@@ -2575,7 +3330,7 @@
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>7</v>
+        <v>45</v>
       </c>
       <c r="C20">
         <v>539</v>
@@ -2655,7 +3410,7 @@
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>11</v>
+        <v>46</v>
       </c>
       <c r="C21">
         <v>1060</v>
@@ -2735,7 +3490,7 @@
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>17</v>
+        <v>47</v>
       </c>
       <c r="C22">
         <v>784</v>
@@ -2815,7 +3570,7 @@
         <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>18</v>
+        <v>48</v>
       </c>
       <c r="C23">
         <v>802</v>
@@ -2895,7 +3650,7 @@
         <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>19</v>
+        <v>49</v>
       </c>
       <c r="C24">
         <v>782</v>
@@ -2975,7 +3730,7 @@
         <v>23</v>
       </c>
       <c r="B25" t="s">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="C25">
         <v>528</v>
@@ -3055,7 +3810,7 @@
         <v>24</v>
       </c>
       <c r="B26" t="s">
-        <v>21</v>
+        <v>51</v>
       </c>
       <c r="C26">
         <v>581</v>
@@ -3135,7 +3890,7 @@
         <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>22</v>
+        <v>52</v>
       </c>
       <c r="C27">
         <v>690</v>
@@ -3215,7 +3970,7 @@
         <v>26</v>
       </c>
       <c r="B28" t="s">
-        <v>23</v>
+        <v>53</v>
       </c>
       <c r="C28">
         <v>785</v>
@@ -3295,7 +4050,7 @@
         <v>27</v>
       </c>
       <c r="B29" t="s">
-        <v>13</v>
+        <v>54</v>
       </c>
       <c r="C29">
         <v>1103</v>
@@ -3375,7 +4130,7 @@
         <v>28</v>
       </c>
       <c r="B30" t="s">
-        <v>14</v>
+        <v>55</v>
       </c>
       <c r="C30">
         <v>1067</v>
@@ -3455,7 +4210,7 @@
         <v>29</v>
       </c>
       <c r="B31" t="s">
-        <v>24</v>
+        <v>56</v>
       </c>
       <c r="C31">
         <v>869</v>
@@ -3535,7 +4290,7 @@
         <v>30</v>
       </c>
       <c r="B32" t="s">
-        <v>25</v>
+        <v>57</v>
       </c>
       <c r="C32">
         <v>916</v>
@@ -3615,7 +4370,7 @@
         <v>31</v>
       </c>
       <c r="B33" t="s">
-        <v>26</v>
+        <v>58</v>
       </c>
       <c r="C33">
         <v>746</v>
@@ -3695,7 +4450,7 @@
         <v>32</v>
       </c>
       <c r="B34" t="s">
-        <v>27</v>
+        <v>59</v>
       </c>
       <c r="C34">
         <v>843</v>
@@ -3775,7 +4530,7 @@
         <v>33</v>
       </c>
       <c r="B35" t="s">
-        <v>28</v>
+        <v>60</v>
       </c>
       <c r="C35">
         <v>653</v>
@@ -3855,7 +4610,7 @@
         <v>34</v>
       </c>
       <c r="B36" t="s">
-        <v>29</v>
+        <v>61</v>
       </c>
       <c r="C36">
         <v>822</v>
@@ -3935,7 +4690,7 @@
         <v>35</v>
       </c>
       <c r="B37" t="s">
-        <v>24</v>
+        <v>62</v>
       </c>
       <c r="C37">
         <v>918</v>
@@ -4015,7 +4770,7 @@
         <v>36</v>
       </c>
       <c r="B38" t="s">
-        <v>25</v>
+        <v>63</v>
       </c>
       <c r="C38">
         <v>1040</v>
@@ -4095,7 +4850,7 @@
         <v>37</v>
       </c>
       <c r="B39" t="s">
-        <v>30</v>
+        <v>64</v>
       </c>
       <c r="C39">
         <v>870</v>
@@ -4175,7 +4930,7 @@
         <v>38</v>
       </c>
       <c r="B40" t="s">
-        <v>31</v>
+        <v>65</v>
       </c>
       <c r="C40">
         <v>1055</v>
@@ -4255,7 +5010,7 @@
         <v>39</v>
       </c>
       <c r="B41" t="s">
-        <v>32</v>
+        <v>66</v>
       </c>
       <c r="C41">
         <v>954</v>
@@ -4335,7 +5090,7 @@
         <v>40</v>
       </c>
       <c r="B42" t="s">
-        <v>33</v>
+        <v>67</v>
       </c>
       <c r="C42">
         <v>777</v>
@@ -4415,7 +5170,7 @@
         <v>41</v>
       </c>
       <c r="B43" t="s">
-        <v>34</v>
+        <v>68</v>
       </c>
       <c r="C43">
         <v>764</v>
@@ -4495,7 +5250,7 @@
         <v>42</v>
       </c>
       <c r="B44" t="s">
-        <v>35</v>
+        <v>69</v>
       </c>
       <c r="C44">
         <v>742</v>
@@ -4575,7 +5330,7 @@
         <v>43</v>
       </c>
       <c r="B45" t="s">
-        <v>30</v>
+        <v>70</v>
       </c>
       <c r="C45">
         <v>926</v>
@@ -4655,7 +5410,7 @@
         <v>44</v>
       </c>
       <c r="B46" t="s">
-        <v>31</v>
+        <v>71</v>
       </c>
       <c r="C46">
         <v>1172</v>
@@ -4735,7 +5490,7 @@
         <v>45</v>
       </c>
       <c r="B47" t="s">
-        <v>36</v>
+        <v>72</v>
       </c>
       <c r="C47">
         <v>944</v>
@@ -4815,7 +5570,7 @@
         <v>46</v>
       </c>
       <c r="B48" t="s">
-        <v>37</v>
+        <v>73</v>
       </c>
       <c r="C48">
         <v>672</v>
@@ -4895,7 +5650,7 @@
         <v>47</v>
       </c>
       <c r="B49" t="s">
-        <v>38</v>
+        <v>74</v>
       </c>
       <c r="C49">
         <v>584</v>
@@ -4975,7 +5730,7 @@
         <v>48</v>
       </c>
       <c r="B50" t="s">
-        <v>39</v>
+        <v>75</v>
       </c>
       <c r="C50">
         <v>1124</v>
@@ -5055,7 +5810,7 @@
         <v>49</v>
       </c>
       <c r="B51" t="s">
-        <v>40</v>
+        <v>76</v>
       </c>
       <c r="C51">
         <v>764</v>
@@ -5135,7 +5890,7 @@
         <v>50</v>
       </c>
       <c r="B52" t="s">
-        <v>41</v>
+        <v>77</v>
       </c>
       <c r="C52">
         <v>1101</v>
@@ -5215,7 +5970,7 @@
         <v>51</v>
       </c>
       <c r="B53" t="s">
-        <v>42</v>
+        <v>78</v>
       </c>
       <c r="C53">
         <v>1144</v>
@@ -5295,7 +6050,7 @@
         <v>52</v>
       </c>
       <c r="B54" t="s">
-        <v>43</v>
+        <v>79</v>
       </c>
       <c r="C54">
         <v>1122</v>
@@ -5375,7 +6130,7 @@
         <v>53</v>
       </c>
       <c r="B55" t="s">
-        <v>44</v>
+        <v>80</v>
       </c>
       <c r="C55">
         <v>886</v>
@@ -5455,7 +6210,7 @@
         <v>54</v>
       </c>
       <c r="B56" t="s">
-        <v>45</v>
+        <v>81</v>
       </c>
       <c r="C56">
         <v>1004</v>
@@ -5535,7 +6290,7 @@
         <v>55</v>
       </c>
       <c r="B57" t="s">
-        <v>46</v>
+        <v>82</v>
       </c>
       <c r="C57">
         <v>1042</v>
@@ -5615,7 +6370,7 @@
         <v>56</v>
       </c>
       <c r="B58" t="s">
-        <v>46</v>
+        <v>83</v>
       </c>
       <c r="C58">
         <v>872</v>
@@ -5695,7 +6450,7 @@
         <v>57</v>
       </c>
       <c r="B59" t="s">
-        <v>47</v>
+        <v>84</v>
       </c>
       <c r="C59">
         <v>962</v>
@@ -5775,7 +6530,7 @@
         <v>58</v>
       </c>
       <c r="B60" t="s">
-        <v>48</v>
+        <v>85</v>
       </c>
       <c r="C60">
         <v>829</v>
@@ -5855,7 +6610,7 @@
         <v>59</v>
       </c>
       <c r="B61" t="s">
-        <v>49</v>
+        <v>86</v>
       </c>
       <c r="C61">
         <v>1111</v>
@@ -5935,7 +6690,7 @@
         <v>60</v>
       </c>
       <c r="B62" t="s">
-        <v>50</v>
+        <v>87</v>
       </c>
       <c r="C62">
         <v>823</v>
@@ -6015,7 +6770,7 @@
         <v>61</v>
       </c>
       <c r="B63" t="s">
-        <v>51</v>
+        <v>88</v>
       </c>
       <c r="C63">
         <v>378</v>
@@ -6095,7 +6850,7 @@
         <v>62</v>
       </c>
       <c r="B64" t="s">
-        <v>52</v>
+        <v>89</v>
       </c>
       <c r="C64">
         <v>643</v>
@@ -6175,7 +6930,7 @@
         <v>63</v>
       </c>
       <c r="B65" t="s">
-        <v>53</v>
+        <v>90</v>
       </c>
       <c r="C65">
         <v>768</v>
@@ -6255,7 +7010,7 @@
         <v>64</v>
       </c>
       <c r="B66" t="s">
-        <v>54</v>
+        <v>91</v>
       </c>
       <c r="C66">
         <v>890</v>
@@ -6335,7 +7090,7 @@
         <v>65</v>
       </c>
       <c r="B67" t="s">
-        <v>55</v>
+        <v>92</v>
       </c>
       <c r="C67">
         <v>556</v>
@@ -6415,7 +7170,7 @@
         <v>66</v>
       </c>
       <c r="B68" t="s">
-        <v>56</v>
+        <v>93</v>
       </c>
       <c r="C68">
         <v>1034</v>
@@ -6495,7 +7250,7 @@
         <v>67</v>
       </c>
       <c r="B69" t="s">
-        <v>57</v>
+        <v>94</v>
       </c>
       <c r="C69">
         <v>651</v>
@@ -6575,7 +7330,7 @@
         <v>68</v>
       </c>
       <c r="B70" t="s">
-        <v>58</v>
+        <v>95</v>
       </c>
       <c r="C70">
         <v>670</v>
@@ -6655,7 +7410,7 @@
         <v>69</v>
       </c>
       <c r="B71" t="s">
-        <v>59</v>
+        <v>96</v>
       </c>
       <c r="C71">
         <v>783</v>
@@ -6735,7 +7490,7 @@
         <v>70</v>
       </c>
       <c r="B72" t="s">
-        <v>60</v>
+        <v>97</v>
       </c>
       <c r="C72">
         <v>730</v>
@@ -6815,7 +7570,7 @@
         <v>71</v>
       </c>
       <c r="B73" t="s">
-        <v>61</v>
+        <v>98</v>
       </c>
       <c r="C73">
         <v>522</v>
@@ -6895,7 +7650,7 @@
         <v>72</v>
       </c>
       <c r="B74" t="s">
-        <v>48</v>
+        <v>99</v>
       </c>
       <c r="C74">
         <v>659</v>
@@ -6975,7 +7730,7 @@
         <v>73</v>
       </c>
       <c r="B75" t="s">
-        <v>49</v>
+        <v>100</v>
       </c>
       <c r="C75">
         <v>634</v>
@@ -7055,7 +7810,7 @@
         <v>74</v>
       </c>
       <c r="B76" t="s">
-        <v>62</v>
+        <v>101</v>
       </c>
       <c r="C76">
         <v>884</v>
@@ -7135,7 +7890,7 @@
         <v>75</v>
       </c>
       <c r="B77" t="s">
-        <v>63</v>
+        <v>102</v>
       </c>
       <c r="C77">
         <v>736</v>
@@ -7215,7 +7970,7 @@
         <v>76</v>
       </c>
       <c r="B78" t="s">
-        <v>64</v>
+        <v>103</v>
       </c>
       <c r="C78">
         <v>723</v>
@@ -7295,7 +8050,7 @@
         <v>77</v>
       </c>
       <c r="B79" t="s">
-        <v>65</v>
+        <v>104</v>
       </c>
       <c r="C79">
         <v>445</v>
@@ -7375,7 +8130,7 @@
         <v>78</v>
       </c>
       <c r="B80" t="s">
-        <v>66</v>
+        <v>105</v>
       </c>
       <c r="C80">
         <v>742</v>
@@ -7455,7 +8210,7 @@
         <v>79</v>
       </c>
       <c r="B81" t="s">
-        <v>67</v>
+        <v>106</v>
       </c>
       <c r="C81">
         <v>641</v>
@@ -7535,7 +8290,7 @@
         <v>80</v>
       </c>
       <c r="B82" t="s">
-        <v>63</v>
+        <v>107</v>
       </c>
       <c r="C82">
         <v>1043</v>
@@ -7615,7 +8370,7 @@
         <v>81</v>
       </c>
       <c r="B83" t="s">
-        <v>68</v>
+        <v>108</v>
       </c>
       <c r="C83">
         <v>1127</v>
@@ -7695,7 +8450,7 @@
         <v>82</v>
       </c>
       <c r="B84" t="s">
-        <v>69</v>
+        <v>109</v>
       </c>
       <c r="C84">
         <v>856</v>
@@ -7775,7 +8530,7 @@
         <v>83</v>
       </c>
       <c r="B85" t="s">
-        <v>70</v>
+        <v>110</v>
       </c>
       <c r="C85">
         <v>860</v>
@@ -7855,7 +8610,7 @@
         <v>84</v>
       </c>
       <c r="B86" t="s">
-        <v>71</v>
+        <v>111</v>
       </c>
       <c r="C86">
         <v>942</v>
@@ -7935,7 +8690,7 @@
         <v>85</v>
       </c>
       <c r="B87" t="s">
-        <v>48</v>
+        <v>112</v>
       </c>
       <c r="C87">
         <v>836</v>
@@ -8015,7 +8770,7 @@
         <v>86</v>
       </c>
       <c r="B88" t="s">
-        <v>49</v>
+        <v>113</v>
       </c>
       <c r="C88">
         <v>718</v>
@@ -8095,7 +8850,7 @@
         <v>87</v>
       </c>
       <c r="B89" t="s">
-        <v>48</v>
+        <v>114</v>
       </c>
       <c r="C89">
         <v>838</v>
@@ -8175,7 +8930,7 @@
         <v>88</v>
       </c>
       <c r="B90" t="s">
-        <v>49</v>
+        <v>115</v>
       </c>
       <c r="C90">
         <v>988</v>
@@ -8255,7 +9010,7 @@
         <v>89</v>
       </c>
       <c r="B91" t="s">
-        <v>48</v>
+        <v>116</v>
       </c>
       <c r="C91">
         <v>633</v>
@@ -8335,7 +9090,7 @@
         <v>90</v>
       </c>
       <c r="B92" t="s">
-        <v>49</v>
+        <v>117</v>
       </c>
       <c r="C92">
         <v>787</v>
@@ -8415,7 +9170,7 @@
         <v>91</v>
       </c>
       <c r="B93" t="s">
-        <v>72</v>
+        <v>118</v>
       </c>
       <c r="C93">
         <v>913</v>
@@ -8495,7 +9250,7 @@
         <v>92</v>
       </c>
       <c r="B94" t="s">
-        <v>73</v>
+        <v>119</v>
       </c>
       <c r="C94">
         <v>1031</v>
@@ -8575,7 +9330,7 @@
         <v>93</v>
       </c>
       <c r="B95" t="s">
-        <v>74</v>
+        <v>120</v>
       </c>
       <c r="C95">
         <v>928</v>
@@ -8655,7 +9410,7 @@
         <v>94</v>
       </c>
       <c r="B96" t="s">
-        <v>75</v>
+        <v>121</v>
       </c>
       <c r="C96">
         <v>695</v>
@@ -8735,7 +9490,7 @@
         <v>95</v>
       </c>
       <c r="B97" t="s">
-        <v>76</v>
+        <v>122</v>
       </c>
       <c r="C97">
         <v>702</v>
@@ -8815,7 +9570,7 @@
         <v>96</v>
       </c>
       <c r="B98" t="s">
-        <v>77</v>
+        <v>123</v>
       </c>
       <c r="C98">
         <v>1071</v>
@@ -8895,7 +9650,7 @@
         <v>97</v>
       </c>
       <c r="B99" t="s">
-        <v>78</v>
+        <v>124</v>
       </c>
       <c r="C99">
         <v>539</v>
@@ -8975,7 +9730,7 @@
         <v>98</v>
       </c>
       <c r="B100" t="s">
-        <v>79</v>
+        <v>125</v>
       </c>
       <c r="C100">
         <v>532</v>
@@ -9055,7 +9810,7 @@
         <v>99</v>
       </c>
       <c r="B101" t="s">
-        <v>80</v>
+        <v>126</v>
       </c>
       <c r="C101">
         <v>566</v>
@@ -9135,7 +9890,7 @@
         <v>100</v>
       </c>
       <c r="B102" t="s">
-        <v>81</v>
+        <v>127</v>
       </c>
       <c r="C102">
         <v>590</v>
@@ -9215,7 +9970,7 @@
         <v>101</v>
       </c>
       <c r="B103" t="s">
-        <v>82</v>
+        <v>128</v>
       </c>
       <c r="C103">
         <v>1037</v>
@@ -9295,7 +10050,7 @@
         <v>102</v>
       </c>
       <c r="B104" t="s">
-        <v>80</v>
+        <v>129</v>
       </c>
       <c r="C104">
         <v>966</v>
@@ -9375,7 +10130,7 @@
         <v>103</v>
       </c>
       <c r="B105" t="s">
-        <v>20</v>
+        <v>130</v>
       </c>
       <c r="C105">
         <v>810</v>
@@ -9455,7 +10210,7 @@
         <v>104</v>
       </c>
       <c r="B106" t="s">
-        <v>77</v>
+        <v>131</v>
       </c>
       <c r="C106">
         <v>775</v>
@@ -9535,7 +10290,7 @@
         <v>105</v>
       </c>
       <c r="B107" t="s">
-        <v>78</v>
+        <v>132</v>
       </c>
       <c r="C107">
         <v>586</v>
@@ -9615,7 +10370,7 @@
         <v>106</v>
       </c>
       <c r="B108" t="s">
-        <v>21</v>
+        <v>133</v>
       </c>
       <c r="C108">
         <v>1000</v>
@@ -9695,7 +10450,7 @@
         <v>107</v>
       </c>
       <c r="B109" t="s">
-        <v>79</v>
+        <v>134</v>
       </c>
       <c r="C109">
         <v>693</v>
@@ -9775,7 +10530,7 @@
         <v>108</v>
       </c>
       <c r="B110" t="s">
-        <v>48</v>
+        <v>135</v>
       </c>
       <c r="C110">
         <v>1077</v>
@@ -9855,7 +10610,7 @@
         <v>109</v>
       </c>
       <c r="B111" t="s">
-        <v>49</v>
+        <v>136</v>
       </c>
       <c r="C111">
         <v>1051</v>
@@ -9935,7 +10690,7 @@
         <v>110</v>
       </c>
       <c r="B112" t="s">
-        <v>80</v>
+        <v>137</v>
       </c>
       <c r="C112">
         <v>656</v>
@@ -10015,7 +10770,7 @@
         <v>111</v>
       </c>
       <c r="B113" t="s">
-        <v>83</v>
+        <v>138</v>
       </c>
       <c r="C113">
         <v>1109</v>
@@ -10095,7 +10850,7 @@
         <v>112</v>
       </c>
       <c r="B114" t="s">
-        <v>84</v>
+        <v>139</v>
       </c>
       <c r="C114">
         <v>1109</v>
@@ -10175,7 +10930,7 @@
         <v>113</v>
       </c>
       <c r="B115" t="s">
-        <v>85</v>
+        <v>140</v>
       </c>
       <c r="C115">
         <v>1002</v>
@@ -10255,7 +11010,7 @@
         <v>114</v>
       </c>
       <c r="B116" t="s">
-        <v>86</v>
+        <v>141</v>
       </c>
       <c r="C116">
         <v>1047</v>
@@ -10335,7 +11090,7 @@
         <v>115</v>
       </c>
       <c r="B117" t="s">
-        <v>87</v>
+        <v>142</v>
       </c>
       <c r="C117">
         <v>641</v>
@@ -10415,7 +11170,7 @@
         <v>116</v>
       </c>
       <c r="B118" t="s">
-        <v>88</v>
+        <v>143</v>
       </c>
       <c r="C118">
         <v>800</v>
@@ -10495,7 +11250,7 @@
         <v>117</v>
       </c>
       <c r="B119" t="s">
-        <v>89</v>
+        <v>144</v>
       </c>
       <c r="C119">
         <v>977</v>
@@ -10575,7 +11330,7 @@
         <v>118</v>
       </c>
       <c r="B120" t="s">
-        <v>90</v>
+        <v>145</v>
       </c>
       <c r="C120">
         <v>453</v>
@@ -10655,7 +11410,7 @@
         <v>119</v>
       </c>
       <c r="B121" t="s">
-        <v>21</v>
+        <v>146</v>
       </c>
       <c r="C121">
         <v>1128</v>
@@ -10735,7 +11490,7 @@
         <v>120</v>
       </c>
       <c r="B122" t="s">
-        <v>91</v>
+        <v>147</v>
       </c>
       <c r="C122">
         <v>1068</v>
@@ -10815,7 +11570,7 @@
         <v>121</v>
       </c>
       <c r="B123" t="s">
-        <v>92</v>
+        <v>148</v>
       </c>
       <c r="C123">
         <v>864</v>
@@ -10895,7 +11650,7 @@
         <v>122</v>
       </c>
       <c r="B124" t="s">
-        <v>93</v>
+        <v>149</v>
       </c>
       <c r="C124">
         <v>371</v>
@@ -10975,7 +11730,7 @@
         <v>123</v>
       </c>
       <c r="B125" t="s">
-        <v>94</v>
+        <v>150</v>
       </c>
       <c r="C125">
         <v>998</v>
@@ -11055,7 +11810,7 @@
         <v>124</v>
       </c>
       <c r="B126" t="s">
-        <v>95</v>
+        <v>151</v>
       </c>
       <c r="C126">
         <v>710</v>
@@ -11135,7 +11890,7 @@
         <v>125</v>
       </c>
       <c r="B127" t="s">
-        <v>63</v>
+        <v>152</v>
       </c>
       <c r="C127">
         <v>865</v>
@@ -11215,7 +11970,7 @@
         <v>126</v>
       </c>
       <c r="B128" t="s">
-        <v>86</v>
+        <v>153</v>
       </c>
       <c r="C128">
         <v>895</v>
@@ -11295,7 +12050,7 @@
         <v>127</v>
       </c>
       <c r="B129" t="s">
-        <v>63</v>
+        <v>154</v>
       </c>
       <c r="C129">
         <v>914</v>
@@ -11375,7 +12130,7 @@
         <v>128</v>
       </c>
       <c r="B130" t="s">
-        <v>21</v>
+        <v>155</v>
       </c>
       <c r="C130">
         <v>930</v>
@@ -11455,7 +12210,7 @@
         <v>129</v>
       </c>
       <c r="B131" t="s">
-        <v>96</v>
+        <v>156</v>
       </c>
       <c r="C131">
         <v>566</v>
@@ -11535,7 +12290,7 @@
         <v>130</v>
       </c>
       <c r="B132" t="s">
-        <v>80</v>
+        <v>157</v>
       </c>
       <c r="C132">
         <v>1021</v>
@@ -11615,7 +12370,7 @@
         <v>131</v>
       </c>
       <c r="B133" t="s">
-        <v>76</v>
+        <v>158</v>
       </c>
       <c r="C133">
         <v>704</v>
@@ -11695,7 +12450,7 @@
         <v>132</v>
       </c>
       <c r="B134" t="s">
-        <v>80</v>
+        <v>159</v>
       </c>
       <c r="C134">
         <v>479</v>
@@ -11775,7 +12530,7 @@
         <v>133</v>
       </c>
       <c r="B135" t="s">
-        <v>97</v>
+        <v>160</v>
       </c>
       <c r="C135">
         <v>555</v>
@@ -11855,7 +12610,7 @@
         <v>134</v>
       </c>
       <c r="B136" t="s">
-        <v>98</v>
+        <v>161</v>
       </c>
       <c r="C136">
         <v>1158</v>
@@ -11935,7 +12690,7 @@
         <v>135</v>
       </c>
       <c r="B137" t="s">
-        <v>99</v>
+        <v>162</v>
       </c>
       <c r="C137">
         <v>589</v>
@@ -12015,7 +12770,7 @@
         <v>136</v>
       </c>
       <c r="B138" t="s">
-        <v>80</v>
+        <v>163</v>
       </c>
       <c r="C138">
         <v>859</v>
@@ -12095,7 +12850,7 @@
         <v>137</v>
       </c>
       <c r="B139" t="s">
-        <v>100</v>
+        <v>164</v>
       </c>
       <c r="C139">
         <v>1133</v>
@@ -12175,7 +12930,7 @@
         <v>138</v>
       </c>
       <c r="B140" t="s">
-        <v>79</v>
+        <v>165</v>
       </c>
       <c r="C140">
         <v>787</v>
@@ -12255,7 +13010,7 @@
         <v>139</v>
       </c>
       <c r="B141" t="s">
-        <v>13</v>
+        <v>166</v>
       </c>
       <c r="C141">
         <v>1005</v>
@@ -12335,7 +13090,7 @@
         <v>140</v>
       </c>
       <c r="B142" t="s">
-        <v>14</v>
+        <v>167</v>
       </c>
       <c r="C142">
         <v>1056</v>
@@ -12415,7 +13170,7 @@
         <v>141</v>
       </c>
       <c r="B143" t="s">
-        <v>101</v>
+        <v>168</v>
       </c>
       <c r="C143">
         <v>1135</v>
@@ -12495,7 +13250,7 @@
         <v>142</v>
       </c>
       <c r="B144" t="s">
-        <v>102</v>
+        <v>169</v>
       </c>
       <c r="C144">
         <v>1113</v>
@@ -12575,7 +13330,7 @@
         <v>143</v>
       </c>
       <c r="B145" t="s">
-        <v>103</v>
+        <v>170</v>
       </c>
       <c r="C145">
         <v>673</v>
@@ -12655,7 +13410,7 @@
         <v>144</v>
       </c>
       <c r="B146" t="s">
-        <v>104</v>
+        <v>171</v>
       </c>
       <c r="C146">
         <v>779</v>
@@ -12735,7 +13490,7 @@
         <v>145</v>
       </c>
       <c r="B147" t="s">
-        <v>80</v>
+        <v>172</v>
       </c>
       <c r="C147">
         <v>1104</v>
@@ -12815,7 +13570,7 @@
         <v>146</v>
       </c>
       <c r="B148" t="s">
-        <v>48</v>
+        <v>173</v>
       </c>
       <c r="C148">
         <v>1018</v>
@@ -12895,7 +13650,7 @@
         <v>147</v>
       </c>
       <c r="B149" t="s">
-        <v>49</v>
+        <v>174</v>
       </c>
       <c r="C149">
         <v>941</v>
@@ -12975,7 +13730,7 @@
         <v>148</v>
       </c>
       <c r="B150" t="s">
-        <v>7</v>
+        <v>175</v>
       </c>
       <c r="C150">
         <v>962</v>
@@ -13055,7 +13810,7 @@
         <v>149</v>
       </c>
       <c r="B151" t="s">
-        <v>105</v>
+        <v>176</v>
       </c>
       <c r="C151">
         <v>519</v>
@@ -13135,7 +13890,7 @@
         <v>150</v>
       </c>
       <c r="B152" t="s">
-        <v>89</v>
+        <v>177</v>
       </c>
       <c r="C152">
         <v>421</v>
@@ -13215,7 +13970,7 @@
         <v>151</v>
       </c>
       <c r="B153" t="s">
-        <v>90</v>
+        <v>178</v>
       </c>
       <c r="C153">
         <v>1153</v>
@@ -13295,7 +14050,7 @@
         <v>152</v>
       </c>
       <c r="B154" t="s">
-        <v>102</v>
+        <v>179</v>
       </c>
       <c r="C154">
         <v>802</v>
@@ -13375,7 +14130,7 @@
         <v>153</v>
       </c>
       <c r="B155" t="s">
-        <v>87</v>
+        <v>180</v>
       </c>
       <c r="C155">
         <v>635</v>
@@ -13455,7 +14210,7 @@
         <v>154</v>
       </c>
       <c r="B156" t="s">
-        <v>88</v>
+        <v>181</v>
       </c>
       <c r="C156">
         <v>736</v>
@@ -13535,7 +14290,7 @@
         <v>155</v>
       </c>
       <c r="B157" t="s">
-        <v>80</v>
+        <v>182</v>
       </c>
       <c r="C157">
         <v>970</v>
@@ -13615,7 +14370,7 @@
         <v>156</v>
       </c>
       <c r="B158" t="s">
-        <v>80</v>
+        <v>183</v>
       </c>
       <c r="C158">
         <v>767</v>
@@ -13695,7 +14450,7 @@
         <v>157</v>
       </c>
       <c r="B159" t="s">
-        <v>106</v>
+        <v>184</v>
       </c>
       <c r="C159">
         <v>662</v>
@@ -13775,7 +14530,7 @@
         <v>158</v>
       </c>
       <c r="B160" t="s">
-        <v>107</v>
+        <v>185</v>
       </c>
       <c r="C160">
         <v>728</v>
@@ -13855,7 +14610,7 @@
         <v>159</v>
       </c>
       <c r="B161" t="s">
-        <v>108</v>
+        <v>186</v>
       </c>
       <c r="C161">
         <v>663</v>
@@ -13935,7 +14690,7 @@
         <v>160</v>
       </c>
       <c r="B162" t="s">
-        <v>93</v>
+        <v>187</v>
       </c>
       <c r="C162">
         <v>601</v>
@@ -14015,7 +14770,7 @@
         <v>161</v>
       </c>
       <c r="B163" t="s">
-        <v>109</v>
+        <v>188</v>
       </c>
       <c r="C163">
         <v>719</v>
@@ -14095,7 +14850,7 @@
         <v>162</v>
       </c>
       <c r="B164" t="s">
-        <v>110</v>
+        <v>189</v>
       </c>
       <c r="C164">
         <v>633</v>
@@ -14175,7 +14930,7 @@
         <v>163</v>
       </c>
       <c r="B165" t="s">
-        <v>111</v>
+        <v>190</v>
       </c>
       <c r="C165">
         <v>714</v>
@@ -14255,7 +15010,7 @@
         <v>164</v>
       </c>
       <c r="B166" t="s">
-        <v>112</v>
+        <v>191</v>
       </c>
       <c r="C166">
         <v>750</v>
@@ -14335,7 +15090,7 @@
         <v>165</v>
       </c>
       <c r="B167" t="s">
-        <v>86</v>
+        <v>192</v>
       </c>
       <c r="C167">
         <v>929</v>
@@ -14415,7 +15170,7 @@
         <v>166</v>
       </c>
       <c r="B168" t="s">
-        <v>113</v>
+        <v>193</v>
       </c>
       <c r="C168">
         <v>613</v>
@@ -14495,7 +15250,7 @@
         <v>167</v>
       </c>
       <c r="B169" t="s">
-        <v>114</v>
+        <v>194</v>
       </c>
       <c r="C169">
         <v>909</v>
@@ -14575,7 +15330,7 @@
         <v>168</v>
       </c>
       <c r="B170" t="s">
-        <v>115</v>
+        <v>195</v>
       </c>
       <c r="C170">
         <v>757</v>
@@ -14655,7 +15410,7 @@
         <v>169</v>
       </c>
       <c r="B171" t="s">
-        <v>80</v>
+        <v>196</v>
       </c>
       <c r="C171">
         <v>1080</v>
@@ -14735,7 +15490,7 @@
         <v>170</v>
       </c>
       <c r="B172" t="s">
-        <v>80</v>
+        <v>197</v>
       </c>
       <c r="C172">
         <v>561</v>
@@ -14815,7 +15570,7 @@
         <v>171</v>
       </c>
       <c r="B173" t="s">
-        <v>116</v>
+        <v>198</v>
       </c>
       <c r="C173">
         <v>497</v>
@@ -14895,7 +15650,7 @@
         <v>172</v>
       </c>
       <c r="B174" t="s">
-        <v>102</v>
+        <v>199</v>
       </c>
       <c r="C174">
         <v>647</v>
@@ -14975,7 +15730,7 @@
         <v>173</v>
       </c>
       <c r="B175" t="s">
-        <v>21</v>
+        <v>200</v>
       </c>
       <c r="C175">
         <v>531</v>
@@ -15055,7 +15810,7 @@
         <v>174</v>
       </c>
       <c r="B176" t="s">
-        <v>117</v>
+        <v>201</v>
       </c>
       <c r="C176">
         <v>763</v>
@@ -15135,7 +15890,7 @@
         <v>175</v>
       </c>
       <c r="B177" t="s">
-        <v>118</v>
+        <v>202</v>
       </c>
       <c r="C177">
         <v>606</v>
@@ -15215,7 +15970,7 @@
         <v>176</v>
       </c>
       <c r="B178" t="s">
-        <v>119</v>
+        <v>203</v>
       </c>
       <c r="C178">
         <v>722</v>
@@ -15295,7 +16050,7 @@
         <v>177</v>
       </c>
       <c r="B179" t="s">
-        <v>120</v>
+        <v>204</v>
       </c>
       <c r="C179">
         <v>904</v>
@@ -15375,7 +16130,7 @@
         <v>178</v>
       </c>
       <c r="B180" t="s">
-        <v>121</v>
+        <v>205</v>
       </c>
       <c r="C180">
         <v>879</v>
@@ -15455,7 +16210,7 @@
         <v>179</v>
       </c>
       <c r="B181" t="s">
-        <v>122</v>
+        <v>206</v>
       </c>
       <c r="C181">
         <v>1101</v>
@@ -15535,7 +16290,7 @@
         <v>180</v>
       </c>
       <c r="B182" t="s">
-        <v>89</v>
+        <v>207</v>
       </c>
       <c r="C182">
         <v>788</v>
@@ -15615,7 +16370,7 @@
         <v>181</v>
       </c>
       <c r="B183" t="s">
-        <v>90</v>
+        <v>208</v>
       </c>
       <c r="C183">
         <v>1069</v>
@@ -15695,7 +16450,7 @@
         <v>182</v>
       </c>
       <c r="B184" t="s">
-        <v>123</v>
+        <v>209</v>
       </c>
       <c r="C184">
         <v>888</v>
@@ -15775,7 +16530,7 @@
         <v>183</v>
       </c>
       <c r="B185" t="s">
-        <v>22</v>
+        <v>210</v>
       </c>
       <c r="C185">
         <v>1114</v>
@@ -15855,7 +16610,7 @@
         <v>184</v>
       </c>
       <c r="B186" t="s">
-        <v>124</v>
+        <v>211</v>
       </c>
       <c r="C186">
         <v>914</v>
@@ -15935,7 +16690,7 @@
         <v>185</v>
       </c>
       <c r="B187" t="s">
-        <v>125</v>
+        <v>212</v>
       </c>
       <c r="C187">
         <v>1136</v>
@@ -16015,7 +16770,7 @@
         <v>186</v>
       </c>
       <c r="B188" t="s">
-        <v>126</v>
+        <v>213</v>
       </c>
       <c r="C188">
         <v>1155</v>
@@ -16095,7 +16850,7 @@
         <v>187</v>
       </c>
       <c r="B189" t="s">
-        <v>127</v>
+        <v>214</v>
       </c>
       <c r="C189">
         <v>496</v>
@@ -16175,7 +16930,7 @@
         <v>188</v>
       </c>
       <c r="B190" t="s">
-        <v>128</v>
+        <v>215</v>
       </c>
       <c r="C190">
         <v>890</v>
@@ -16255,7 +17010,7 @@
         <v>189</v>
       </c>
       <c r="B191" t="s">
-        <v>21</v>
+        <v>216</v>
       </c>
       <c r="C191">
         <v>861</v>
@@ -16335,7 +17090,7 @@
         <v>190</v>
       </c>
       <c r="B192" t="s">
-        <v>60</v>
+        <v>217</v>
       </c>
       <c r="C192">
         <v>686</v>
@@ -16415,7 +17170,7 @@
         <v>191</v>
       </c>
       <c r="B193" t="s">
-        <v>61</v>
+        <v>218</v>
       </c>
       <c r="C193">
         <v>608</v>
@@ -16495,7 +17250,7 @@
         <v>192</v>
       </c>
       <c r="B194" t="s">
-        <v>80</v>
+        <v>219</v>
       </c>
       <c r="C194">
         <v>737</v>
@@ -16575,7 +17330,7 @@
         <v>193</v>
       </c>
       <c r="B195" t="s">
-        <v>129</v>
+        <v>220</v>
       </c>
       <c r="C195">
         <v>1184</v>
@@ -16655,7 +17410,7 @@
         <v>194</v>
       </c>
       <c r="B196" t="s">
-        <v>130</v>
+        <v>221</v>
       </c>
       <c r="C196">
         <v>983</v>
@@ -16735,7 +17490,7 @@
         <v>195</v>
       </c>
       <c r="B197" t="s">
-        <v>131</v>
+        <v>222</v>
       </c>
       <c r="C197">
         <v>980</v>
@@ -16815,7 +17570,7 @@
         <v>196</v>
       </c>
       <c r="B198" t="s">
-        <v>132</v>
+        <v>223</v>
       </c>
       <c r="C198">
         <v>1043</v>
@@ -16895,7 +17650,7 @@
         <v>197</v>
       </c>
       <c r="B199" t="s">
-        <v>133</v>
+        <v>224</v>
       </c>
       <c r="C199">
         <v>1085</v>
@@ -16975,7 +17730,7 @@
         <v>198</v>
       </c>
       <c r="B200" t="s">
-        <v>134</v>
+        <v>225</v>
       </c>
       <c r="C200">
         <v>1158</v>
@@ -17055,7 +17810,7 @@
         <v>199</v>
       </c>
       <c r="B201" t="s">
-        <v>117</v>
+        <v>226</v>
       </c>
       <c r="C201">
         <v>1148</v>
@@ -17135,7 +17890,7 @@
         <v>200</v>
       </c>
       <c r="B202" t="s">
-        <v>118</v>
+        <v>227</v>
       </c>
       <c r="C202">
         <v>861</v>
@@ -17215,7 +17970,7 @@
         <v>201</v>
       </c>
       <c r="B203" t="s">
-        <v>135</v>
+        <v>228</v>
       </c>
       <c r="C203">
         <v>898</v>
@@ -17295,7 +18050,7 @@
         <v>202</v>
       </c>
       <c r="B204" t="s">
-        <v>136</v>
+        <v>229</v>
       </c>
       <c r="C204">
         <v>747</v>
@@ -17375,7 +18130,7 @@
         <v>203</v>
       </c>
       <c r="B205" t="s">
-        <v>137</v>
+        <v>230</v>
       </c>
       <c r="C205">
         <v>719</v>
@@ -17455,7 +18210,7 @@
         <v>204</v>
       </c>
       <c r="B206" t="s">
-        <v>138</v>
+        <v>231</v>
       </c>
       <c r="C206">
         <v>649</v>
@@ -17535,7 +18290,7 @@
         <v>205</v>
       </c>
       <c r="B207" t="s">
-        <v>139</v>
+        <v>232</v>
       </c>
       <c r="C207">
         <v>1086</v>
@@ -17615,7 +18370,7 @@
         <v>206</v>
       </c>
       <c r="B208" t="s">
-        <v>140</v>
+        <v>233</v>
       </c>
       <c r="C208">
         <v>910</v>
@@ -17695,7 +18450,7 @@
         <v>207</v>
       </c>
       <c r="B209" t="s">
-        <v>141</v>
+        <v>234</v>
       </c>
       <c r="C209">
         <v>700</v>
@@ -17775,7 +18530,7 @@
         <v>208</v>
       </c>
       <c r="B210" t="s">
-        <v>142</v>
+        <v>235</v>
       </c>
       <c r="C210">
         <v>655</v>
@@ -17855,7 +18610,7 @@
         <v>209</v>
       </c>
       <c r="B211" t="s">
-        <v>143</v>
+        <v>236</v>
       </c>
       <c r="C211">
         <v>810</v>
@@ -17935,7 +18690,7 @@
         <v>210</v>
       </c>
       <c r="B212" t="s">
-        <v>144</v>
+        <v>237</v>
       </c>
       <c r="C212">
         <v>797</v>
@@ -18015,7 +18770,7 @@
         <v>211</v>
       </c>
       <c r="B213" t="s">
-        <v>145</v>
+        <v>238</v>
       </c>
       <c r="C213">
         <v>1117</v>
@@ -18095,7 +18850,7 @@
         <v>212</v>
       </c>
       <c r="B214" t="s">
-        <v>146</v>
+        <v>239</v>
       </c>
       <c r="C214">
         <v>902</v>
@@ -18175,7 +18930,7 @@
         <v>213</v>
       </c>
       <c r="B215" t="s">
-        <v>147</v>
+        <v>240</v>
       </c>
       <c r="C215">
         <v>989</v>
@@ -18255,7 +19010,7 @@
         <v>214</v>
       </c>
       <c r="B216" t="s">
-        <v>145</v>
+        <v>241</v>
       </c>
       <c r="C216">
         <v>1072</v>
@@ -18335,7 +19090,7 @@
         <v>215</v>
       </c>
       <c r="B217" t="s">
-        <v>146</v>
+        <v>242</v>
       </c>
       <c r="C217">
         <v>1093</v>
@@ -18415,7 +19170,7 @@
         <v>216</v>
       </c>
       <c r="B218" t="s">
-        <v>147</v>
+        <v>243</v>
       </c>
       <c r="C218">
         <v>1082</v>
@@ -18495,7 +19250,7 @@
         <v>217</v>
       </c>
       <c r="B219" t="s">
-        <v>148</v>
+        <v>244</v>
       </c>
       <c r="C219">
         <v>1113</v>
@@ -18575,7 +19330,7 @@
         <v>218</v>
       </c>
       <c r="B220" t="s">
-        <v>149</v>
+        <v>245</v>
       </c>
       <c r="C220">
         <v>1134</v>
@@ -18655,7 +19410,7 @@
         <v>219</v>
       </c>
       <c r="B221" t="s">
-        <v>150</v>
+        <v>246</v>
       </c>
       <c r="C221">
         <v>1164</v>
@@ -18735,7 +19490,7 @@
         <v>220</v>
       </c>
       <c r="B222" t="s">
-        <v>151</v>
+        <v>247</v>
       </c>
       <c r="C222">
         <v>812</v>
@@ -18815,7 +19570,7 @@
         <v>221</v>
       </c>
       <c r="B223" t="s">
-        <v>152</v>
+        <v>248</v>
       </c>
       <c r="C223">
         <v>829</v>
@@ -18895,7 +19650,7 @@
         <v>222</v>
       </c>
       <c r="B224" t="s">
-        <v>153</v>
+        <v>249</v>
       </c>
       <c r="C224">
         <v>811</v>
@@ -18975,7 +19730,7 @@
         <v>223</v>
       </c>
       <c r="B225" t="s">
-        <v>154</v>
+        <v>250</v>
       </c>
       <c r="C225">
         <v>1105</v>
@@ -19055,7 +19810,7 @@
         <v>224</v>
       </c>
       <c r="B226" t="s">
-        <v>155</v>
+        <v>251</v>
       </c>
       <c r="C226">
         <v>542</v>
@@ -19135,7 +19890,7 @@
         <v>225</v>
       </c>
       <c r="B227" t="s">
-        <v>156</v>
+        <v>252</v>
       </c>
       <c r="C227">
         <v>924</v>
@@ -19215,7 +19970,7 @@
         <v>226</v>
       </c>
       <c r="B228" t="s">
-        <v>157</v>
+        <v>253</v>
       </c>
       <c r="C228">
         <v>926</v>
@@ -19295,7 +20050,7 @@
         <v>227</v>
       </c>
       <c r="B229" t="s">
-        <v>158</v>
+        <v>254</v>
       </c>
       <c r="C229">
         <v>799</v>
@@ -19375,7 +20130,7 @@
         <v>228</v>
       </c>
       <c r="B230" t="s">
-        <v>159</v>
+        <v>255</v>
       </c>
       <c r="C230">
         <v>818</v>
@@ -19455,7 +20210,7 @@
         <v>229</v>
       </c>
       <c r="B231" t="s">
-        <v>102</v>
+        <v>256</v>
       </c>
       <c r="C231">
         <v>717</v>
@@ -19535,7 +20290,7 @@
         <v>230</v>
       </c>
       <c r="B232" t="s">
-        <v>102</v>
+        <v>257</v>
       </c>
       <c r="C232">
         <v>724</v>
@@ -19615,7 +20370,7 @@
         <v>231</v>
       </c>
       <c r="B233" t="s">
-        <v>21</v>
+        <v>258</v>
       </c>
       <c r="C233">
         <v>713</v>
@@ -19695,7 +20450,7 @@
         <v>232</v>
       </c>
       <c r="B234" t="s">
-        <v>21</v>
+        <v>259</v>
       </c>
       <c r="C234">
         <v>996</v>
@@ -19775,7 +20530,7 @@
         <v>233</v>
       </c>
       <c r="B235" t="s">
-        <v>21</v>
+        <v>260</v>
       </c>
       <c r="C235">
         <v>717</v>
@@ -19855,7 +20610,7 @@
         <v>234</v>
       </c>
       <c r="B236" t="s">
-        <v>102</v>
+        <v>261</v>
       </c>
       <c r="C236">
         <v>870</v>
@@ -19935,7 +20690,7 @@
         <v>235</v>
       </c>
       <c r="B237" t="s">
-        <v>89</v>
+        <v>262</v>
       </c>
       <c r="C237">
         <v>955</v>
@@ -20015,7 +20770,7 @@
         <v>236</v>
       </c>
       <c r="B238" t="s">
-        <v>90</v>
+        <v>263</v>
       </c>
       <c r="C238">
         <v>1039</v>
@@ -20095,7 +20850,7 @@
         <v>237</v>
       </c>
       <c r="B239" t="s">
-        <v>89</v>
+        <v>264</v>
       </c>
       <c r="C239">
         <v>860</v>
@@ -20175,7 +20930,7 @@
         <v>238</v>
       </c>
       <c r="B240" t="s">
-        <v>90</v>
+        <v>265</v>
       </c>
       <c r="C240">
         <v>849</v>
@@ -20255,7 +21010,7 @@
         <v>239</v>
       </c>
       <c r="B241" t="s">
-        <v>80</v>
+        <v>266</v>
       </c>
       <c r="C241">
         <v>742</v>
@@ -20335,7 +21090,7 @@
         <v>240</v>
       </c>
       <c r="B242" t="s">
-        <v>102</v>
+        <v>267</v>
       </c>
       <c r="C242">
         <v>674</v>
@@ -20415,7 +21170,7 @@
         <v>241</v>
       </c>
       <c r="B243" t="s">
-        <v>160</v>
+        <v>268</v>
       </c>
       <c r="C243">
         <v>843</v>
@@ -20495,7 +21250,7 @@
         <v>242</v>
       </c>
       <c r="B244" t="s">
-        <v>161</v>
+        <v>269</v>
       </c>
       <c r="C244">
         <v>374</v>
@@ -20575,7 +21330,7 @@
         <v>243</v>
       </c>
       <c r="B245" t="s">
-        <v>117</v>
+        <v>270</v>
       </c>
       <c r="C245">
         <v>778</v>
@@ -20655,7 +21410,7 @@
         <v>244</v>
       </c>
       <c r="B246" t="s">
-        <v>118</v>
+        <v>271</v>
       </c>
       <c r="C246">
         <v>721</v>
@@ -20735,7 +21490,7 @@
         <v>245</v>
       </c>
       <c r="B247" t="s">
-        <v>72</v>
+        <v>272</v>
       </c>
       <c r="C247">
         <v>1181</v>
@@ -20815,7 +21570,7 @@
         <v>246</v>
       </c>
       <c r="B248" t="s">
-        <v>162</v>
+        <v>273</v>
       </c>
       <c r="C248">
         <v>934</v>
@@ -20895,7 +21650,7 @@
         <v>247</v>
       </c>
       <c r="B249" t="s">
-        <v>163</v>
+        <v>274</v>
       </c>
       <c r="C249">
         <v>444</v>
@@ -20975,7 +21730,7 @@
         <v>248</v>
       </c>
       <c r="B250" t="s">
-        <v>80</v>
+        <v>275</v>
       </c>
       <c r="C250">
         <v>979</v>
@@ -21055,7 +21810,7 @@
         <v>249</v>
       </c>
       <c r="B251" t="s">
-        <v>160</v>
+        <v>276</v>
       </c>
       <c r="C251">
         <v>714</v>
@@ -21135,7 +21890,7 @@
         <v>250</v>
       </c>
       <c r="B252" t="s">
-        <v>161</v>
+        <v>277</v>
       </c>
       <c r="C252">
         <v>606</v>
@@ -21215,7 +21970,7 @@
         <v>251</v>
       </c>
       <c r="B253" t="s">
-        <v>80</v>
+        <v>278</v>
       </c>
       <c r="C253">
         <v>663</v>
@@ -21295,7 +22050,7 @@
         <v>252</v>
       </c>
       <c r="B254" t="s">
-        <v>164</v>
+        <v>279</v>
       </c>
       <c r="C254">
         <v>1050</v>
@@ -21375,7 +22130,7 @@
         <v>253</v>
       </c>
       <c r="B255" t="s">
-        <v>165</v>
+        <v>280</v>
       </c>
       <c r="C255">
         <v>1088</v>
@@ -21455,7 +22210,7 @@
         <v>254</v>
       </c>
       <c r="B256" t="s">
-        <v>166</v>
+        <v>281</v>
       </c>
       <c r="C256">
         <v>1047</v>
@@ -21535,7 +22290,7 @@
         <v>255</v>
       </c>
       <c r="B257" t="s">
-        <v>167</v>
+        <v>282</v>
       </c>
       <c r="C257">
         <v>534</v>
@@ -21615,7 +22370,7 @@
         <v>256</v>
       </c>
       <c r="B258" t="s">
-        <v>168</v>
+        <v>283</v>
       </c>
       <c r="C258">
         <v>684</v>
@@ -21695,7 +22450,7 @@
         <v>257</v>
       </c>
       <c r="B259" t="s">
-        <v>169</v>
+        <v>284</v>
       </c>
       <c r="C259">
         <v>693</v>
@@ -21775,7 +22530,7 @@
         <v>258</v>
       </c>
       <c r="B260" t="s">
-        <v>170</v>
+        <v>285</v>
       </c>
       <c r="C260">
         <v>1063</v>
@@ -21855,7 +22610,7 @@
         <v>259</v>
       </c>
       <c r="B261" t="s">
-        <v>171</v>
+        <v>286</v>
       </c>
       <c r="C261">
         <v>641</v>
@@ -21935,7 +22690,7 @@
         <v>260</v>
       </c>
       <c r="B262" t="s">
-        <v>21</v>
+        <v>287</v>
       </c>
       <c r="C262">
         <v>1062</v>
@@ -22015,7 +22770,7 @@
         <v>261</v>
       </c>
       <c r="B263" t="s">
-        <v>83</v>
+        <v>288</v>
       </c>
       <c r="C263">
         <v>752</v>
@@ -22095,7 +22850,7 @@
         <v>262</v>
       </c>
       <c r="B264" t="s">
-        <v>84</v>
+        <v>289</v>
       </c>
       <c r="C264">
         <v>745</v>
@@ -22175,7 +22930,7 @@
         <v>263</v>
       </c>
       <c r="B265" t="s">
-        <v>172</v>
+        <v>290</v>
       </c>
       <c r="C265">
         <v>882</v>
@@ -22255,7 +23010,7 @@
         <v>264</v>
       </c>
       <c r="B266" t="s">
-        <v>173</v>
+        <v>291</v>
       </c>
       <c r="C266">
         <v>531</v>
@@ -22335,7 +23090,7 @@
         <v>265</v>
       </c>
       <c r="B267" t="s">
-        <v>76</v>
+        <v>292</v>
       </c>
       <c r="C267">
         <v>861</v>
@@ -22415,7 +23170,7 @@
         <v>266</v>
       </c>
       <c r="B268" t="s">
-        <v>174</v>
+        <v>293</v>
       </c>
       <c r="C268">
         <v>926</v>
@@ -22495,7 +23250,7 @@
         <v>267</v>
       </c>
       <c r="B269" t="s">
-        <v>33</v>
+        <v>294</v>
       </c>
       <c r="C269">
         <v>1005</v>
@@ -22575,7 +23330,7 @@
         <v>268</v>
       </c>
       <c r="B270" t="s">
-        <v>175</v>
+        <v>295</v>
       </c>
       <c r="C270">
         <v>595</v>
@@ -22655,7 +23410,7 @@
         <v>269</v>
       </c>
       <c r="B271" t="s">
-        <v>89</v>
+        <v>296</v>
       </c>
       <c r="C271">
         <v>811</v>
@@ -22735,7 +23490,7 @@
         <v>270</v>
       </c>
       <c r="B272" t="s">
-        <v>90</v>
+        <v>297</v>
       </c>
       <c r="C272">
         <v>585</v>
@@ -22815,7 +23570,7 @@
         <v>271</v>
       </c>
       <c r="B273" t="s">
-        <v>80</v>
+        <v>298</v>
       </c>
       <c r="C273">
         <v>1226</v>
@@ -22895,7 +23650,7 @@
         <v>272</v>
       </c>
       <c r="B274" t="s">
-        <v>80</v>
+        <v>299</v>
       </c>
       <c r="C274">
         <v>676</v>
@@ -22975,7 +23730,7 @@
         <v>273</v>
       </c>
       <c r="B275" t="s">
-        <v>176</v>
+        <v>300</v>
       </c>
       <c r="C275">
         <v>630</v>
@@ -23055,7 +23810,7 @@
         <v>274</v>
       </c>
       <c r="B276" t="s">
-        <v>177</v>
+        <v>301</v>
       </c>
       <c r="C276">
         <v>610</v>
@@ -23135,7 +23890,7 @@
         <v>275</v>
       </c>
       <c r="B277" t="s">
-        <v>87</v>
+        <v>302</v>
       </c>
       <c r="C277">
         <v>1127</v>
@@ -23215,7 +23970,7 @@
         <v>276</v>
       </c>
       <c r="B278" t="s">
-        <v>88</v>
+        <v>303</v>
       </c>
       <c r="C278">
         <v>511</v>
@@ -23295,7 +24050,7 @@
         <v>277</v>
       </c>
       <c r="B279" t="s">
-        <v>86</v>
+        <v>304</v>
       </c>
       <c r="C279">
         <v>847</v>
@@ -23375,7 +24130,7 @@
         <v>278</v>
       </c>
       <c r="B280" t="s">
-        <v>21</v>
+        <v>305</v>
       </c>
       <c r="C280">
         <v>955</v>
@@ -23455,7 +24210,7 @@
         <v>279</v>
       </c>
       <c r="B281" t="s">
-        <v>178</v>
+        <v>306</v>
       </c>
       <c r="C281">
         <v>508</v>
@@ -23535,7 +24290,7 @@
         <v>280</v>
       </c>
       <c r="B282" t="s">
-        <v>102</v>
+        <v>307</v>
       </c>
       <c r="C282">
         <v>657</v>
@@ -23615,7 +24370,7 @@
         <v>281</v>
       </c>
       <c r="B283" t="s">
-        <v>179</v>
+        <v>308</v>
       </c>
       <c r="C283">
         <v>778</v>
@@ -23695,7 +24450,7 @@
         <v>282</v>
       </c>
       <c r="B284" t="s">
-        <v>16</v>
+        <v>309</v>
       </c>
       <c r="C284">
         <v>526</v>
@@ -23775,7 +24530,7 @@
         <v>283</v>
       </c>
       <c r="B285" t="s">
-        <v>180</v>
+        <v>310</v>
       </c>
       <c r="C285">
         <v>516</v>
@@ -23855,7 +24610,7 @@
         <v>284</v>
       </c>
       <c r="B286" t="s">
-        <v>80</v>
+        <v>311</v>
       </c>
       <c r="C286">
         <v>685</v>
@@ -23935,7 +24690,7 @@
         <v>285</v>
       </c>
       <c r="B287" t="s">
-        <v>48</v>
+        <v>312</v>
       </c>
       <c r="C287">
         <v>825</v>
@@ -24015,7 +24770,7 @@
         <v>286</v>
       </c>
       <c r="B288" t="s">
-        <v>49</v>
+        <v>313</v>
       </c>
       <c r="C288">
         <v>766</v>
@@ -24095,7 +24850,7 @@
         <v>287</v>
       </c>
       <c r="B289" t="s">
-        <v>181</v>
+        <v>314</v>
       </c>
       <c r="C289">
         <v>720</v>
@@ -24175,7 +24930,7 @@
         <v>288</v>
       </c>
       <c r="B290" t="s">
-        <v>80</v>
+        <v>315</v>
       </c>
       <c r="C290">
         <v>968</v>
@@ -24255,7 +25010,7 @@
         <v>289</v>
       </c>
       <c r="B291" t="s">
-        <v>182</v>
+        <v>316</v>
       </c>
       <c r="C291">
         <v>631</v>
@@ -24335,7 +25090,7 @@
         <v>290</v>
       </c>
       <c r="B292" t="s">
-        <v>158</v>
+        <v>317</v>
       </c>
       <c r="C292">
         <v>751</v>
@@ -24415,7 +25170,7 @@
         <v>291</v>
       </c>
       <c r="B293" t="s">
-        <v>159</v>
+        <v>318</v>
       </c>
       <c r="C293">
         <v>651</v>
@@ -24495,7 +25250,7 @@
         <v>292</v>
       </c>
       <c r="B294" t="s">
-        <v>183</v>
+        <v>319</v>
       </c>
       <c r="C294">
         <v>831</v>
@@ -24575,7 +25330,7 @@
         <v>293</v>
       </c>
       <c r="B295" t="s">
-        <v>89</v>
+        <v>320</v>
       </c>
       <c r="C295">
         <v>1051</v>
@@ -24655,7 +25410,7 @@
         <v>294</v>
       </c>
       <c r="B296" t="s">
-        <v>90</v>
+        <v>321</v>
       </c>
       <c r="C296">
         <v>727</v>
@@ -24735,7 +25490,7 @@
         <v>295</v>
       </c>
       <c r="B297" t="s">
-        <v>21</v>
+        <v>322</v>
       </c>
       <c r="C297">
         <v>1028</v>
@@ -24815,7 +25570,7 @@
         <v>296</v>
       </c>
       <c r="B298" t="s">
-        <v>184</v>
+        <v>323</v>
       </c>
       <c r="C298">
         <v>1120</v>
@@ -24895,7 +25650,7 @@
         <v>297</v>
       </c>
       <c r="B299" t="s">
-        <v>185</v>
+        <v>324</v>
       </c>
       <c r="C299">
         <v>1025</v>
@@ -24975,7 +25730,7 @@
         <v>298</v>
       </c>
       <c r="B300" t="s">
-        <v>186</v>
+        <v>325</v>
       </c>
       <c r="C300">
         <v>1123</v>
@@ -25055,7 +25810,7 @@
         <v>299</v>
       </c>
       <c r="B301" t="s">
-        <v>187</v>
+        <v>326</v>
       </c>
       <c r="C301">
         <v>627</v>
@@ -25135,7 +25890,7 @@
         <v>300</v>
       </c>
       <c r="B302" t="s">
-        <v>188</v>
+        <v>327</v>
       </c>
       <c r="C302">
         <v>654</v>
@@ -25215,7 +25970,7 @@
         <v>301</v>
       </c>
       <c r="B303" t="s">
-        <v>189</v>
+        <v>328</v>
       </c>
       <c r="C303">
         <v>572</v>
@@ -25295,7 +26050,7 @@
         <v>302</v>
       </c>
       <c r="B304" t="s">
-        <v>48</v>
+        <v>329</v>
       </c>
       <c r="C304">
         <v>854</v>
@@ -25375,7 +26130,7 @@
         <v>303</v>
       </c>
       <c r="B305" t="s">
-        <v>49</v>
+        <v>330</v>
       </c>
       <c r="C305">
         <v>1112</v>
@@ -25455,7 +26210,7 @@
         <v>304</v>
       </c>
       <c r="B306" t="s">
-        <v>100</v>
+        <v>331</v>
       </c>
       <c r="C306">
         <v>1119</v>
@@ -25535,7 +26290,7 @@
         <v>305</v>
       </c>
       <c r="B307" t="s">
-        <v>190</v>
+        <v>332</v>
       </c>
       <c r="C307">
         <v>875</v>
@@ -25615,7 +26370,7 @@
         <v>306</v>
       </c>
       <c r="B308" t="s">
-        <v>191</v>
+        <v>333</v>
       </c>
       <c r="C308">
         <v>894</v>
@@ -25695,7 +26450,7 @@
         <v>307</v>
       </c>
       <c r="B309" t="s">
-        <v>180</v>
+        <v>334</v>
       </c>
       <c r="C309">
         <v>1016</v>
@@ -25775,7 +26530,7 @@
         <v>308</v>
       </c>
       <c r="B310" t="s">
-        <v>192</v>
+        <v>335</v>
       </c>
       <c r="C310">
         <v>925</v>
@@ -25855,7 +26610,7 @@
         <v>309</v>
       </c>
       <c r="B311" t="s">
-        <v>193</v>
+        <v>336</v>
       </c>
       <c r="C311">
         <v>438</v>
@@ -25935,7 +26690,7 @@
         <v>310</v>
       </c>
       <c r="B312" t="s">
-        <v>80</v>
+        <v>337</v>
       </c>
       <c r="C312">
         <v>685</v>
@@ -26015,7 +26770,7 @@
         <v>311</v>
       </c>
       <c r="B313" t="s">
-        <v>194</v>
+        <v>338</v>
       </c>
       <c r="C313">
         <v>789</v>
@@ -26095,7 +26850,7 @@
         <v>312</v>
       </c>
       <c r="B314" t="s">
-        <v>195</v>
+        <v>339</v>
       </c>
       <c r="C314">
         <v>587</v>
@@ -26175,7 +26930,7 @@
         <v>313</v>
       </c>
       <c r="B315" t="s">
-        <v>160</v>
+        <v>340</v>
       </c>
       <c r="C315">
         <v>899</v>
@@ -26255,7 +27010,7 @@
         <v>314</v>
       </c>
       <c r="B316" t="s">
-        <v>161</v>
+        <v>75</v>
       </c>
       <c r="C316">
         <v>506</v>
@@ -26335,7 +27090,7 @@
         <v>315</v>
       </c>
       <c r="B317" t="s">
-        <v>196</v>
+        <v>341</v>
       </c>
       <c r="C317">
         <v>696</v>
@@ -26415,7 +27170,7 @@
         <v>316</v>
       </c>
       <c r="B318" t="s">
-        <v>87</v>
+        <v>342</v>
       </c>
       <c r="C318">
         <v>1202</v>
@@ -26495,7 +27250,7 @@
         <v>317</v>
       </c>
       <c r="B319" t="s">
-        <v>88</v>
+        <v>343</v>
       </c>
       <c r="C319">
         <v>889</v>
@@ -26575,7 +27330,7 @@
         <v>318</v>
       </c>
       <c r="B320" t="s">
-        <v>197</v>
+        <v>344</v>
       </c>
       <c r="C320">
         <v>969</v>
@@ -26655,7 +27410,7 @@
         <v>319</v>
       </c>
       <c r="B321" t="s">
-        <v>198</v>
+        <v>345</v>
       </c>
       <c r="C321">
         <v>1154</v>
@@ -26735,7 +27490,7 @@
         <v>320</v>
       </c>
       <c r="B322" t="s">
-        <v>63</v>
+        <v>346</v>
       </c>
       <c r="C322">
         <v>1155</v>
@@ -26815,7 +27570,7 @@
         <v>321</v>
       </c>
       <c r="B323" t="s">
-        <v>106</v>
+        <v>347</v>
       </c>
       <c r="C323">
         <v>629</v>
@@ -26895,7 +27650,7 @@
         <v>322</v>
       </c>
       <c r="B324" t="s">
-        <v>107</v>
+        <v>348</v>
       </c>
       <c r="C324">
         <v>685</v>
@@ -26975,7 +27730,7 @@
         <v>323</v>
       </c>
       <c r="B325" t="s">
-        <v>102</v>
+        <v>349</v>
       </c>
       <c r="C325">
         <v>803</v>
@@ -27055,7 +27810,7 @@
         <v>324</v>
       </c>
       <c r="B326" t="s">
-        <v>102</v>
+        <v>350</v>
       </c>
       <c r="C326">
         <v>716</v>
@@ -27135,7 +27890,7 @@
         <v>325</v>
       </c>
       <c r="B327" t="s">
-        <v>96</v>
+        <v>351</v>
       </c>
       <c r="C327">
         <v>534</v>
@@ -27215,7 +27970,7 @@
         <v>326</v>
       </c>
       <c r="B328" t="s">
-        <v>199</v>
+        <v>352</v>
       </c>
       <c r="C328">
         <v>596</v>
@@ -27295,7 +28050,7 @@
         <v>327</v>
       </c>
       <c r="B329" t="s">
-        <v>200</v>
+        <v>353</v>
       </c>
       <c r="C329">
         <v>603</v>
@@ -27375,7 +28130,7 @@
         <v>328</v>
       </c>
       <c r="B330" t="s">
-        <v>102</v>
+        <v>354</v>
       </c>
       <c r="C330">
         <v>1003</v>
@@ -27455,7 +28210,7 @@
         <v>329</v>
       </c>
       <c r="B331" t="s">
-        <v>201</v>
+        <v>355</v>
       </c>
       <c r="C331">
         <v>884</v>
@@ -27535,7 +28290,7 @@
         <v>330</v>
       </c>
       <c r="B332" t="s">
-        <v>202</v>
+        <v>356</v>
       </c>
       <c r="C332">
         <v>914</v>
@@ -27615,7 +28370,7 @@
         <v>331</v>
       </c>
       <c r="B333" t="s">
-        <v>203</v>
+        <v>357</v>
       </c>
       <c r="C333">
         <v>563</v>
@@ -27695,7 +28450,7 @@
         <v>332</v>
       </c>
       <c r="B334" t="s">
-        <v>80</v>
+        <v>358</v>
       </c>
       <c r="C334">
         <v>848</v>
@@ -27775,7 +28530,7 @@
         <v>333</v>
       </c>
       <c r="B335" t="s">
-        <v>87</v>
+        <v>359</v>
       </c>
       <c r="C335">
         <v>988</v>
@@ -27855,7 +28610,7 @@
         <v>334</v>
       </c>
       <c r="B336" t="s">
-        <v>88</v>
+        <v>360</v>
       </c>
       <c r="C336">
         <v>709</v>
@@ -27935,7 +28690,7 @@
         <v>335</v>
       </c>
       <c r="B337" t="s">
-        <v>80</v>
+        <v>361</v>
       </c>
       <c r="C337">
         <v>883</v>
@@ -28015,7 +28770,7 @@
         <v>336</v>
       </c>
       <c r="B338" t="s">
-        <v>158</v>
+        <v>362</v>
       </c>
       <c r="C338">
         <v>749</v>
@@ -28095,7 +28850,7 @@
         <v>337</v>
       </c>
       <c r="B339" t="s">
-        <v>159</v>
+        <v>363</v>
       </c>
       <c r="C339">
         <v>822</v>
@@ -28175,7 +28930,7 @@
         <v>338</v>
       </c>
       <c r="B340" t="s">
-        <v>158</v>
+        <v>364</v>
       </c>
       <c r="C340">
         <v>613</v>
@@ -28255,7 +29010,7 @@
         <v>339</v>
       </c>
       <c r="B341" t="s">
-        <v>159</v>
+        <v>365</v>
       </c>
       <c r="C341">
         <v>751</v>
@@ -28335,7 +29090,7 @@
         <v>340</v>
       </c>
       <c r="B342" t="s">
-        <v>7</v>
+        <v>366</v>
       </c>
       <c r="C342">
         <v>538</v>
@@ -28415,7 +29170,7 @@
         <v>341</v>
       </c>
       <c r="B343" t="s">
-        <v>116</v>
+        <v>367</v>
       </c>
       <c r="C343">
         <v>737</v>
@@ -28495,7 +29250,7 @@
         <v>342</v>
       </c>
       <c r="B344" t="s">
-        <v>79</v>
+        <v>368</v>
       </c>
       <c r="C344">
         <v>1077</v>
@@ -28575,7 +29330,7 @@
         <v>343</v>
       </c>
       <c r="B345" t="s">
-        <v>21</v>
+        <v>369</v>
       </c>
       <c r="C345">
         <v>778</v>
@@ -28655,7 +29410,7 @@
         <v>344</v>
       </c>
       <c r="B346" t="s">
-        <v>204</v>
+        <v>370</v>
       </c>
       <c r="C346">
         <v>1049</v>
@@ -28735,7 +29490,7 @@
         <v>345</v>
       </c>
       <c r="B347" t="s">
-        <v>48</v>
+        <v>371</v>
       </c>
       <c r="C347">
         <v>1122</v>
@@ -28815,7 +29570,7 @@
         <v>346</v>
       </c>
       <c r="B348" t="s">
-        <v>49</v>
+        <v>372</v>
       </c>
       <c r="C348">
         <v>1035</v>
@@ -28895,7 +29650,7 @@
         <v>347</v>
       </c>
       <c r="B349" t="s">
-        <v>181</v>
+        <v>373</v>
       </c>
       <c r="C349">
         <v>781</v>
@@ -28975,7 +29730,7 @@
         <v>348</v>
       </c>
       <c r="B350" t="s">
-        <v>205</v>
+        <v>374</v>
       </c>
       <c r="C350">
         <v>424</v>
@@ -29055,7 +29810,7 @@
         <v>349</v>
       </c>
       <c r="B351" t="s">
-        <v>206</v>
+        <v>375</v>
       </c>
       <c r="C351">
         <v>639</v>
@@ -29135,7 +29890,7 @@
         <v>350</v>
       </c>
       <c r="B352" t="s">
-        <v>207</v>
+        <v>376</v>
       </c>
       <c r="C352">
         <v>675</v>
@@ -29215,7 +29970,7 @@
         <v>351</v>
       </c>
       <c r="B353" t="s">
-        <v>83</v>
+        <v>377</v>
       </c>
       <c r="C353">
         <v>994</v>
@@ -29295,7 +30050,7 @@
         <v>352</v>
       </c>
       <c r="B354" t="s">
-        <v>84</v>
+        <v>378</v>
       </c>
       <c r="C354">
         <v>833</v>
@@ -29375,7 +30130,7 @@
         <v>353</v>
       </c>
       <c r="B355" t="s">
-        <v>102</v>
+        <v>379</v>
       </c>
       <c r="C355">
         <v>561</v>
@@ -29455,7 +30210,7 @@
         <v>354</v>
       </c>
       <c r="B356" t="s">
-        <v>180</v>
+        <v>380</v>
       </c>
       <c r="C356">
         <v>877</v>
@@ -29535,7 +30290,7 @@
         <v>355</v>
       </c>
       <c r="B357" t="s">
-        <v>48</v>
+        <v>381</v>
       </c>
       <c r="C357">
         <v>1161</v>
@@ -29615,7 +30370,7 @@
         <v>356</v>
       </c>
       <c r="B358" t="s">
-        <v>49</v>
+        <v>382</v>
       </c>
       <c r="C358">
         <v>1149</v>
@@ -29695,7 +30450,7 @@
         <v>357</v>
       </c>
       <c r="B359" t="s">
-        <v>208</v>
+        <v>383</v>
       </c>
       <c r="C359">
         <v>778</v>
@@ -29775,7 +30530,7 @@
         <v>358</v>
       </c>
       <c r="B360" t="s">
-        <v>209</v>
+        <v>384</v>
       </c>
       <c r="C360">
         <v>680</v>
@@ -29855,7 +30610,7 @@
         <v>359</v>
       </c>
       <c r="B361" t="s">
-        <v>94</v>
+        <v>385</v>
       </c>
       <c r="C361">
         <v>890</v>
@@ -29935,7 +30690,7 @@
         <v>360</v>
       </c>
       <c r="B362" t="s">
-        <v>95</v>
+        <v>386</v>
       </c>
       <c r="C362">
         <v>844</v>
@@ -30015,7 +30770,7 @@
         <v>361</v>
       </c>
       <c r="B363" t="s">
-        <v>210</v>
+        <v>387</v>
       </c>
       <c r="C363">
         <v>466</v>
@@ -30095,7 +30850,7 @@
         <v>362</v>
       </c>
       <c r="B364" t="s">
-        <v>211</v>
+        <v>388</v>
       </c>
       <c r="C364">
         <v>584</v>
@@ -30175,7 +30930,7 @@
         <v>363</v>
       </c>
       <c r="B365" t="s">
-        <v>46</v>
+        <v>389</v>
       </c>
       <c r="C365">
         <v>637</v>
@@ -30255,7 +31010,7 @@
         <v>364</v>
       </c>
       <c r="B366" t="s">
-        <v>212</v>
+        <v>390</v>
       </c>
       <c r="C366">
         <v>1110</v>
@@ -30335,7 +31090,7 @@
         <v>365</v>
       </c>
       <c r="B367" t="s">
-        <v>213</v>
+        <v>391</v>
       </c>
       <c r="C367">
         <v>823</v>
@@ -30415,7 +31170,7 @@
         <v>366</v>
       </c>
       <c r="B368" t="s">
-        <v>77</v>
+        <v>392</v>
       </c>
       <c r="C368">
         <v>618</v>
@@ -30495,7 +31250,7 @@
         <v>367</v>
       </c>
       <c r="B369" t="s">
-        <v>78</v>
+        <v>393</v>
       </c>
       <c r="C369">
         <v>966</v>
@@ -30575,7 +31330,7 @@
         <v>368</v>
       </c>
       <c r="B370" t="s">
-        <v>214</v>
+        <v>394</v>
       </c>
       <c r="C370">
         <v>980</v>
@@ -30655,7 +31410,7 @@
         <v>369</v>
       </c>
       <c r="B371" t="s">
-        <v>215</v>
+        <v>395</v>
       </c>
       <c r="C371">
         <v>614</v>
@@ -30735,7 +31490,7 @@
         <v>370</v>
       </c>
       <c r="B372" t="s">
-        <v>216</v>
+        <v>396</v>
       </c>
       <c r="C372">
         <v>548</v>
@@ -30815,7 +31570,7 @@
         <v>371</v>
       </c>
       <c r="B373" t="s">
-        <v>63</v>
+        <v>397</v>
       </c>
       <c r="C373">
         <v>991</v>
@@ -30895,7 +31650,7 @@
         <v>372</v>
       </c>
       <c r="B374" t="s">
-        <v>127</v>
+        <v>398</v>
       </c>
       <c r="C374">
         <v>990</v>
@@ -30975,7 +31730,7 @@
         <v>373</v>
       </c>
       <c r="B375" t="s">
-        <v>104</v>
+        <v>399</v>
       </c>
       <c r="C375">
         <v>706</v>
@@ -31055,7 +31810,7 @@
         <v>374</v>
       </c>
       <c r="B376" t="s">
-        <v>102</v>
+        <v>400</v>
       </c>
       <c r="C376">
         <v>881</v>
@@ -31135,7 +31890,7 @@
         <v>375</v>
       </c>
       <c r="B377" t="s">
-        <v>217</v>
+        <v>401</v>
       </c>
       <c r="C377">
         <v>1044</v>
@@ -31215,7 +31970,7 @@
         <v>376</v>
       </c>
       <c r="B378" t="s">
-        <v>218</v>
+        <v>402</v>
       </c>
       <c r="C378">
         <v>845</v>
@@ -31295,7 +32050,7 @@
         <v>377</v>
       </c>
       <c r="B379" t="s">
-        <v>63</v>
+        <v>403</v>
       </c>
       <c r="C379">
         <v>1055</v>
@@ -31375,7 +32130,7 @@
         <v>378</v>
       </c>
       <c r="B380" t="s">
-        <v>79</v>
+        <v>404</v>
       </c>
       <c r="C380">
         <v>1097</v>
@@ -31455,7 +32210,7 @@
         <v>379</v>
       </c>
       <c r="B381" t="s">
-        <v>87</v>
+        <v>405</v>
       </c>
       <c r="C381">
         <v>826</v>
@@ -31535,7 +32290,7 @@
         <v>380</v>
       </c>
       <c r="B382" t="s">
-        <v>88</v>
+        <v>406</v>
       </c>
       <c r="C382">
         <v>883</v>
@@ -31615,7 +32370,7 @@
         <v>381</v>
       </c>
       <c r="B383" t="s">
-        <v>87</v>
+        <v>407</v>
       </c>
       <c r="C383">
         <v>834</v>
@@ -31695,7 +32450,7 @@
         <v>382</v>
       </c>
       <c r="B384" t="s">
-        <v>88</v>
+        <v>408</v>
       </c>
       <c r="C384">
         <v>855</v>
@@ -31775,7 +32530,7 @@
         <v>383</v>
       </c>
       <c r="B385" t="s">
-        <v>80</v>
+        <v>409</v>
       </c>
       <c r="C385">
         <v>1080</v>
@@ -31855,7 +32610,7 @@
         <v>384</v>
       </c>
       <c r="B386" t="s">
-        <v>63</v>
+        <v>410</v>
       </c>
       <c r="C386">
         <v>1017</v>
@@ -31935,7 +32690,7 @@
         <v>385</v>
       </c>
       <c r="B387" t="s">
-        <v>80</v>
+        <v>411</v>
       </c>
       <c r="C387">
         <v>740</v>
@@ -32015,7 +32770,7 @@
         <v>386</v>
       </c>
       <c r="B388" t="s">
-        <v>72</v>
+        <v>412</v>
       </c>
       <c r="C388">
         <v>1140</v>
@@ -32095,7 +32850,7 @@
         <v>387</v>
       </c>
       <c r="B389" t="s">
-        <v>162</v>
+        <v>413</v>
       </c>
       <c r="C389">
         <v>858</v>
@@ -32175,7 +32930,7 @@
         <v>388</v>
       </c>
       <c r="B390" t="s">
-        <v>219</v>
+        <v>414</v>
       </c>
       <c r="C390">
         <v>881</v>
@@ -32255,7 +33010,7 @@
         <v>389</v>
       </c>
       <c r="B391" t="s">
-        <v>21</v>
+        <v>415</v>
       </c>
       <c r="C391">
         <v>681</v>
@@ -32335,7 +33090,7 @@
         <v>390</v>
       </c>
       <c r="B392" t="s">
-        <v>220</v>
+        <v>416</v>
       </c>
       <c r="C392">
         <v>845</v>
@@ -32415,7 +33170,7 @@
         <v>391</v>
       </c>
       <c r="B393" t="s">
-        <v>221</v>
+        <v>417</v>
       </c>
       <c r="C393">
         <v>1015</v>
@@ -32495,7 +33250,7 @@
         <v>392</v>
       </c>
       <c r="B394" t="s">
-        <v>222</v>
+        <v>418</v>
       </c>
       <c r="C394">
         <v>707</v>
@@ -32575,7 +33330,7 @@
         <v>393</v>
       </c>
       <c r="B395" t="s">
-        <v>223</v>
+        <v>419</v>
       </c>
       <c r="C395">
         <v>1035</v>
@@ -32655,7 +33410,7 @@
         <v>394</v>
       </c>
       <c r="B396" t="s">
-        <v>224</v>
+        <v>420</v>
       </c>
       <c r="C396">
         <v>572</v>
@@ -32735,7 +33490,7 @@
         <v>395</v>
       </c>
       <c r="B397" t="s">
-        <v>63</v>
+        <v>421</v>
       </c>
       <c r="C397">
         <v>676</v>
@@ -32815,7 +33570,7 @@
         <v>396</v>
       </c>
       <c r="B398" t="s">
-        <v>83</v>
+        <v>422</v>
       </c>
       <c r="C398">
         <v>1019</v>
@@ -32895,7 +33650,7 @@
         <v>397</v>
       </c>
       <c r="B399" t="s">
-        <v>84</v>
+        <v>423</v>
       </c>
       <c r="C399">
         <v>377</v>
@@ -32975,7 +33730,7 @@
         <v>398</v>
       </c>
       <c r="B400" t="s">
-        <v>80</v>
+        <v>424</v>
       </c>
       <c r="C400">
         <v>890</v>
@@ -33055,7 +33810,7 @@
         <v>399</v>
       </c>
       <c r="B401" t="s">
-        <v>225</v>
+        <v>425</v>
       </c>
       <c r="C401">
         <v>1162</v>
@@ -33135,7 +33890,7 @@
         <v>400</v>
       </c>
       <c r="B402" t="s">
-        <v>226</v>
+        <v>426</v>
       </c>
       <c r="C402">
         <v>633</v>
@@ -33215,7 +33970,7 @@
         <v>401</v>
       </c>
       <c r="B403" t="s">
-        <v>227</v>
+        <v>427</v>
       </c>
       <c r="C403">
         <v>636</v>
@@ -33295,7 +34050,7 @@
         <v>402</v>
       </c>
       <c r="B404" t="s">
-        <v>63</v>
+        <v>428</v>
       </c>
       <c r="C404">
         <v>876</v>
@@ -33375,7 +34130,7 @@
         <v>403</v>
       </c>
       <c r="B405" t="s">
-        <v>102</v>
+        <v>429</v>
       </c>
       <c r="C405">
         <v>1121</v>
@@ -33455,7 +34210,7 @@
         <v>404</v>
       </c>
       <c r="B406" t="s">
-        <v>80</v>
+        <v>430</v>
       </c>
       <c r="C406">
         <v>875</v>
@@ -33535,7 +34290,7 @@
         <v>405</v>
       </c>
       <c r="B407" t="s">
-        <v>180</v>
+        <v>431</v>
       </c>
       <c r="C407">
         <v>934</v>
@@ -33615,7 +34370,7 @@
         <v>406</v>
       </c>
       <c r="B408" t="s">
-        <v>228</v>
+        <v>432</v>
       </c>
       <c r="C408">
         <v>772</v>
@@ -33695,7 +34450,7 @@
         <v>407</v>
       </c>
       <c r="B409" t="s">
-        <v>229</v>
+        <v>433</v>
       </c>
       <c r="C409">
         <v>683</v>
@@ -33775,7 +34530,7 @@
         <v>408</v>
       </c>
       <c r="B410" t="s">
-        <v>77</v>
+        <v>434</v>
       </c>
       <c r="C410">
         <v>928</v>
@@ -33855,7 +34610,7 @@
         <v>409</v>
       </c>
       <c r="B411" t="s">
-        <v>78</v>
+        <v>435</v>
       </c>
       <c r="C411">
         <v>974</v>
@@ -33935,7 +34690,7 @@
         <v>410</v>
       </c>
       <c r="B412" t="s">
-        <v>116</v>
+        <v>436</v>
       </c>
       <c r="C412">
         <v>818</v>
@@ -34015,7 +34770,7 @@
         <v>411</v>
       </c>
       <c r="B413" t="s">
-        <v>102</v>
+        <v>437</v>
       </c>
       <c r="C413">
         <v>605</v>
@@ -34095,7 +34850,7 @@
         <v>412</v>
       </c>
       <c r="B414" t="s">
-        <v>158</v>
+        <v>438</v>
       </c>
       <c r="C414">
         <v>1081</v>
@@ -34175,7 +34930,7 @@
         <v>413</v>
       </c>
       <c r="B415" t="s">
-        <v>159</v>
+        <v>439</v>
       </c>
       <c r="C415">
         <v>975</v>
@@ -34255,7 +35010,7 @@
         <v>414</v>
       </c>
       <c r="B416" t="s">
-        <v>13</v>
+        <v>440</v>
       </c>
       <c r="C416">
         <v>916</v>
@@ -34335,7 +35090,7 @@
         <v>415</v>
       </c>
       <c r="B417" t="s">
-        <v>14</v>
+        <v>441</v>
       </c>
       <c r="C417">
         <v>887</v>
@@ -34415,7 +35170,7 @@
         <v>416</v>
       </c>
       <c r="B418" t="s">
-        <v>158</v>
+        <v>442</v>
       </c>
       <c r="C418">
         <v>1082</v>
@@ -34495,7 +35250,7 @@
         <v>417</v>
       </c>
       <c r="B419" t="s">
-        <v>159</v>
+        <v>443</v>
       </c>
       <c r="C419">
         <v>1125</v>
@@ -34575,7 +35330,7 @@
         <v>418</v>
       </c>
       <c r="B420" t="s">
-        <v>230</v>
+        <v>444</v>
       </c>
       <c r="C420">
         <v>808</v>
@@ -34655,7 +35410,7 @@
         <v>419</v>
       </c>
       <c r="B421" t="s">
-        <v>79</v>
+        <v>445</v>
       </c>
       <c r="C421">
         <v>1056</v>
@@ -34735,7 +35490,7 @@
         <v>420</v>
       </c>
       <c r="B422" t="s">
-        <v>231</v>
+        <v>446</v>
       </c>
       <c r="C422">
         <v>1109</v>
@@ -34815,7 +35570,7 @@
         <v>421</v>
       </c>
       <c r="B423" t="s">
-        <v>124</v>
+        <v>447</v>
       </c>
       <c r="C423">
         <v>861</v>
@@ -34895,7 +35650,7 @@
         <v>422</v>
       </c>
       <c r="B424" t="s">
-        <v>127</v>
+        <v>448</v>
       </c>
       <c r="C424">
         <v>496</v>
@@ -34975,7 +35730,7 @@
         <v>423</v>
       </c>
       <c r="B425" t="s">
-        <v>232</v>
+        <v>449</v>
       </c>
       <c r="C425">
         <v>865</v>
@@ -35055,7 +35810,7 @@
         <v>424</v>
       </c>
       <c r="B426" t="s">
-        <v>233</v>
+        <v>450</v>
       </c>
       <c r="C426">
         <v>511</v>
@@ -35135,7 +35890,7 @@
         <v>425</v>
       </c>
       <c r="B427" t="s">
-        <v>234</v>
+        <v>451</v>
       </c>
       <c r="C427">
         <v>858</v>
@@ -35215,7 +35970,7 @@
         <v>426</v>
       </c>
       <c r="B428" t="s">
-        <v>235</v>
+        <v>452</v>
       </c>
       <c r="C428">
         <v>768</v>
@@ -35295,7 +36050,7 @@
         <v>427</v>
       </c>
       <c r="B429" t="s">
-        <v>21</v>
+        <v>453</v>
       </c>
       <c r="C429">
         <v>554</v>
